--- a/public/data/pedido quimicos campaña 2026 valorizado.xlsx
+++ b/public/data/pedido quimicos campaña 2026 valorizado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fincalaseis-my.sharepoint.com/personal/compras_fincalaseis_com_ar/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2128" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA27411A-0DBB-4F44-8860-72249C31148D}"/>
+  <xr:revisionPtr revIDLastSave="2139" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B499144-2D6E-461C-B738-EC87E607FECB}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{8EF26D9B-9BDD-40EA-9926-EAD75B18C35F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8EF26D9B-9BDD-40EA-9926-EAD75B18C35F}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId13"/>
+    <pivotCache cacheId="187" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="197">
   <si>
     <t>Solicita</t>
   </si>
@@ -649,6 +649,12 @@
   <si>
     <t>R-1-1265</t>
   </si>
+  <si>
+    <t>Equipo de Sal a granel</t>
+  </si>
+  <si>
+    <t>R-1-42253</t>
+  </si>
 </sst>
 </file>
 
@@ -883,7 +889,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -963,13 +969,21 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 3" xfId="2" xr:uid="{1D32B0D1-24D0-4CD1-BA07-AB849F504D40}"/>
   </cellStyles>
-  <dxfs count="46">
+  <dxfs count="47">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4594,7 +4608,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:F21" firstHeaderRow="0" firstDataRow="1" firstDataCol="4"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5229,7 +5243,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="36">
+    <format dxfId="37">
       <pivotArea outline="0" fieldPosition="0">
         <references count="5">
           <reference field="4294967294" count="1" selected="0">
@@ -5248,7 +5262,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="35">
+    <format dxfId="36">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5261,7 +5275,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="35">
       <pivotArea outline="0" fieldPosition="0">
         <references count="5">
           <reference field="4294967294" count="1" selected="0">
@@ -5301,7 +5315,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:F22" firstHeaderRow="0" firstDataRow="1" firstDataCol="4"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5953,7 +5967,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="33">
+    <format dxfId="34">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5965,7 +5979,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
+    <format dxfId="33">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5973,6 +5987,15 @@
           </reference>
           <reference field="7" count="1" selected="0" defaultSubtotal="1">
             <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="32">
+      <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -5996,15 +6019,6 @@
       </pivotArea>
     </format>
     <format dxfId="29">
-      <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="28">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -6013,7 +6027,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -6036,7 +6050,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:D22" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -6659,7 +6673,7 @@
     <dataField name="Suma de Cantidad" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="26">
+    <format dxfId="27">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4" count="0" selected="0"/>
@@ -6679,7 +6693,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="26">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1" selected="0">
@@ -6688,7 +6702,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="25">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4" count="1" selected="0">
@@ -6720,7 +6734,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:G22" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -7418,7 +7432,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="23">
+    <format dxfId="24">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -7427,7 +7441,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="23">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -7450,7 +7464,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:G71" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -8285,7 +8299,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="21">
+    <format dxfId="22">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -8297,7 +8311,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="21">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -8305,6 +8319,15 @@
           </reference>
           <reference field="7" count="1" selected="0" defaultSubtotal="1">
             <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="20">
+      <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -8328,15 +8351,6 @@
       </pivotArea>
     </format>
     <format dxfId="17">
-      <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="16">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8345,7 +8359,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8368,7 +8382,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:E54" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -9142,6 +9156,15 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="5">
+    <format dxfId="15">
+      <pivotArea field="7" grandRow="1" outline="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
     <format dxfId="14">
       <pivotArea field="7" grandRow="1" outline="0">
         <references count="1">
@@ -9161,15 +9184,6 @@
       </pivotArea>
     </format>
     <format dxfId="12">
-      <pivotArea field="7" grandRow="1" outline="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="11">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -9178,7 +9192,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -9201,7 +9215,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -9887,33 +9901,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}" name="Tabla1" displayName="Tabla1" ref="A9:S119" totalsRowShown="0" headerRowDxfId="45">
-  <autoFilter ref="A9:S119" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}" name="Tabla1" displayName="Tabla1" ref="A9:S120" totalsRowShown="0" headerRowDxfId="46">
+  <autoFilter ref="A9:S120" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:S119">
     <sortCondition ref="O9:O119"/>
   </sortState>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{ABC9D6B9-B435-44A8-AC1D-3A7F3684B351}" name="Solicita"/>
-    <tableColumn id="2" xr3:uid="{D6EB60C5-1C40-47ED-9FB1-374E19B24E9A}" name="Fecha" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{D6EB60C5-1C40-47ED-9FB1-374E19B24E9A}" name="Fecha" dataDxfId="45"/>
     <tableColumn id="3" xr3:uid="{D0A4671C-530D-455C-9B7A-52F52FA87E23}" name="Rubro"/>
     <tableColumn id="4" xr3:uid="{E2744C88-A32D-477A-A488-E2EEDE9A0D41}" name="Cantidad"/>
     <tableColumn id="5" xr3:uid="{681C651D-E929-4B0E-B5D7-68CE0CD4311A}" name="U/M"/>
     <tableColumn id="6" xr3:uid="{FD6A41E2-5215-422B-AB72-C8073C73180D}" name="Articulo"/>
     <tableColumn id="7" xr3:uid="{D3D27FF5-A21A-484B-8256-6DC392426D15}" name="Proveedor"/>
     <tableColumn id="8" xr3:uid="{B7EE972F-E2DD-462D-A500-A25FF2470135}" name="Sector"/>
-    <tableColumn id="9" xr3:uid="{02FC2EEA-023E-4B2F-B485-DC353A71EC23}" name="Moneda" dataDxfId="43">
+    <tableColumn id="9" xr3:uid="{02FC2EEA-023E-4B2F-B485-DC353A71EC23}" name="Moneda" dataDxfId="44">
       <calculatedColumnFormula>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[[Descripcion]:[Moneda]],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{DD121184-680A-4A3A-BF4B-A9D24FF92624}" name="$" dataCellStyle="Moneda">
       <calculatedColumnFormula>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{1E29690A-AD00-49F3-AB46-FD0AF8DCE7AE}" name="Importe" dataDxfId="42" dataCellStyle="Moneda">
+    <tableColumn id="18" xr3:uid="{1E29690A-AD00-49F3-AB46-FD0AF8DCE7AE}" name="Importe" dataDxfId="43" dataCellStyle="Moneda">
       <calculatedColumnFormula>IF(I10="$", J10/$H$1, IF(I10="U$D", J10*1, 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{0C4F4870-64EC-4168-97BE-8674B96B82BB}" name="Total" dataDxfId="41" dataCellStyle="Moneda">
+    <tableColumn id="19" xr3:uid="{0C4F4870-64EC-4168-97BE-8674B96B82BB}" name="Total" dataDxfId="42" dataCellStyle="Moneda">
       <calculatedColumnFormula>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2EA38B46-DCBE-4340-A2A4-DD6B043C95F4}" name="Fecha Entrega" dataDxfId="40"/>
+    <tableColumn id="11" xr3:uid="{2EA38B46-DCBE-4340-A2A4-DD6B043C95F4}" name="Fecha Entrega" dataDxfId="41"/>
     <tableColumn id="12" xr3:uid="{4DC2766A-D25F-4018-B804-F35119E17C75}" name="Mes">
       <calculatedColumnFormula>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</calculatedColumnFormula>
     </tableColumn>
@@ -9928,31 +9942,31 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BF6A21D0-BF74-405C-816D-FF180DA65A53}" name="Tabla2" displayName="Tabla2" ref="A2:D18" totalsRowShown="0" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BF6A21D0-BF74-405C-816D-FF180DA65A53}" name="Tabla2" displayName="Tabla2" ref="A2:D18" totalsRowShown="0" headerRowDxfId="40">
   <autoFilter ref="A2:D18" xr:uid="{BF6A21D0-BF74-405C-816D-FF180DA65A53}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4C9ED8A6-DE10-4FC9-A1A8-C9C31853D309}" name="Descripcion" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{4C9ED8A6-DE10-4FC9-A1A8-C9C31853D309}" name="Descripcion" dataDxfId="39"/>
     <tableColumn id="2" xr3:uid="{17F4999B-AFFB-423F-81FC-E94D2D51FCC4}" name="U/M"/>
     <tableColumn id="4" xr3:uid="{AED66179-0481-4D19-8718-F67F09D2A74F}" name="Moneda"/>
-    <tableColumn id="3" xr3:uid="{8D449BA5-7410-4173-AB96-0B1F4A36CC9F}" name="$" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{8D449BA5-7410-4173-AB96-0B1F4A36CC9F}" name="$" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EB8C7E4-857A-45C7-8640-F7ED83B0E987}" name="Tabla3" displayName="Tabla3" ref="B2:H15" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EB8C7E4-857A-45C7-8640-F7ED83B0E987}" name="Tabla3" displayName="Tabla3" ref="B2:H15" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="B2:H15" xr:uid="{8EB8C7E4-857A-45C7-8640-F7ED83B0E987}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{48393E8F-75FE-4E2C-B5A6-0DA171776A4D}" name="Fecha" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{963F1D5B-BEA1-44D4-93E6-186C3DBEAC18}" name="Tipo" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{193244C5-51AA-4CBE-9C5C-987B16E24CCC}" name="Comprobante" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{8FFB7E5E-DF58-448C-A2B8-F8E260D7153A}" name="TN" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{87858EB0-F199-426F-9BD2-3508F9DACC9D}" name="$" dataDxfId="3" dataCellStyle="Moneda"/>
-    <tableColumn id="5" xr3:uid="{DC37D9EF-761A-4BBE-A4AB-069249B5CE73}" name="$Total" dataDxfId="2" dataCellStyle="Moneda">
+    <tableColumn id="1" xr3:uid="{48393E8F-75FE-4E2C-B5A6-0DA171776A4D}" name="Fecha" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{963F1D5B-BEA1-44D4-93E6-186C3DBEAC18}" name="Tipo" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{193244C5-51AA-4CBE-9C5C-987B16E24CCC}" name="Comprobante" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{8FFB7E5E-DF58-448C-A2B8-F8E260D7153A}" name="TN" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{87858EB0-F199-426F-9BD2-3508F9DACC9D}" name="$" dataDxfId="4" dataCellStyle="Moneda"/>
+    <tableColumn id="5" xr3:uid="{DC37D9EF-761A-4BBE-A4AB-069249B5CE73}" name="$Total" dataDxfId="3" dataCellStyle="Moneda">
       <calculatedColumnFormula>F3*E3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{66202679-348D-4EC3-8EBB-E8E14B182F31}" name="$IVA" dataDxfId="1" dataCellStyle="Moneda">
+    <tableColumn id="6" xr3:uid="{66202679-348D-4EC3-8EBB-E8E14B182F31}" name="$IVA" dataDxfId="2" dataCellStyle="Moneda">
       <calculatedColumnFormula>G3*1.21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10281,7 +10295,7 @@
     <tabColor theme="6"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S119"/>
+  <dimension ref="A1:S120"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -10334,11 +10348,11 @@
       </c>
       <c r="K3" s="27">
         <f>SUM(L3:M3)</f>
-        <v>314252.21052631584</v>
+        <v>316296.13157894742</v>
       </c>
       <c r="L3" s="28">
         <f>SUMIFS(L:L, H:H, "INSUMOS DE CAMPAÑA", O:O, "Cumplido")</f>
-        <v>314048.21052631584</v>
+        <v>316092.13157894742</v>
       </c>
       <c r="M3" s="29">
         <f>SUMIFS(L:L, H:H, "INSUMOS DE CAMPAÑA", O:O, "Pendiente")</f>
@@ -10373,11 +10387,11 @@
       </c>
       <c r="K6" s="34">
         <f>SUM(K3:K5)</f>
-        <v>433475.24232631584</v>
+        <v>435519.16337894741</v>
       </c>
       <c r="L6" s="34">
         <f>SUM(L3:L5)</f>
-        <v>366704.72232631582</v>
+        <v>368748.6433789474</v>
       </c>
       <c r="M6" s="35">
         <f>SUM(M3:M5)</f>
@@ -10390,11 +10404,11 @@
       </c>
       <c r="K7" s="36">
         <f>K6*H1</f>
-        <v>658882368.33600008</v>
+        <v>661989128.33600008</v>
       </c>
       <c r="L7" s="36">
         <f>L6*H1</f>
-        <v>557391177.93600011</v>
+        <v>560497937.93599999</v>
       </c>
       <c r="M7" s="37">
         <f>M6*H1</f>
@@ -16777,9 +16791,64 @@
         <v>24</v>
       </c>
     </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>17</v>
+      </c>
+      <c r="B120" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C120" t="s">
+        <v>18</v>
+      </c>
+      <c r="D120">
+        <v>30.76</v>
+      </c>
+      <c r="E120" t="s">
+        <v>129</v>
+      </c>
+      <c r="F120" t="s">
+        <v>195</v>
+      </c>
+      <c r="G120" t="s">
+        <v>40</v>
+      </c>
+      <c r="H120" t="s">
+        <v>83</v>
+      </c>
+      <c r="I120" s="3" t="str">
+        <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[[Descripcion]:[Moneda]],3,FALSE)</f>
+        <v>$</v>
+      </c>
+      <c r="J120" s="2">
+        <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</f>
+        <v>101000</v>
+      </c>
+      <c r="K120" s="43">
+        <f>IF(I120="$", J120/$H$1, IF(I120="U$D", J120*1, 0))</f>
+        <v>66.44736842105263</v>
+      </c>
+      <c r="L120" s="43">
+        <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
+        <v>2043.921052631579</v>
+      </c>
+      <c r="M120" s="1">
+        <v>46254</v>
+      </c>
+      <c r="N120" t="str">
+        <f>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</f>
+        <v>agosto</v>
+      </c>
+      <c r="O120" t="s">
+        <v>31</v>
+      </c>
+      <c r="P120" t="s">
+        <v>196</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A10:P119">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="A10:P120">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$O10="cumplido"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/public/data/pedido quimicos campaña 2026 valorizado.xlsx
+++ b/public/data/pedido quimicos campaña 2026 valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fincalaseis-my.sharepoint.com/personal/compras_fincalaseis_com_ar/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2139" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B499144-2D6E-461C-B738-EC87E607FECB}"/>
+  <xr:revisionPtr revIDLastSave="2147" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A388310B-85C3-4D27-9D9C-1D672D274C90}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8EF26D9B-9BDD-40EA-9926-EAD75B18C35F}"/>
   </bookViews>
@@ -32,7 +32,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="187" r:id="rId13"/>
+    <pivotCache cacheId="31" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="198">
   <si>
     <t>Solicita</t>
   </si>
@@ -655,6 +655,9 @@
   <si>
     <t>R-1-42253</t>
   </si>
+  <si>
+    <t>R-1-512</t>
+  </si>
 </sst>
 </file>
 
@@ -889,7 +892,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -969,21 +972,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 3" xfId="2" xr:uid="{1D32B0D1-24D0-4CD1-BA07-AB849F504D40}"/>
   </cellStyles>
-  <dxfs count="47">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="46">
     <dxf>
       <fill>
         <patternFill>
@@ -1301,22 +1296,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>575272</xdr:colOff>
+      <xdr:colOff>541068</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1070383</xdr:colOff>
+      <xdr:colOff>1059754</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>13804</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
+        <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A017CD1-7551-4D00-BB51-D4282A4C3861}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82E8E167-89B8-67F7-A184-E2A78AC09572}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1332,8 +1327,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6554331" y="188614"/>
-          <a:ext cx="2098329" cy="1192640"/>
+          <a:off x="6520127" y="188615"/>
+          <a:ext cx="2121904" cy="1178836"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4608,7 +4603,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:F21" firstHeaderRow="0" firstDataRow="1" firstDataCol="4"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5243,7 +5238,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="37">
+    <format dxfId="36">
       <pivotArea outline="0" fieldPosition="0">
         <references count="5">
           <reference field="4294967294" count="1" selected="0">
@@ -5262,7 +5257,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="36">
+    <format dxfId="35">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5275,7 +5270,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="35">
+    <format dxfId="34">
       <pivotArea outline="0" fieldPosition="0">
         <references count="5">
           <reference field="4294967294" count="1" selected="0">
@@ -5315,7 +5310,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:F22" firstHeaderRow="0" firstDataRow="1" firstDataCol="4"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5967,7 +5962,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="34">
+    <format dxfId="33">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5979,7 +5974,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="32">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5987,15 +5982,6 @@
           </reference>
           <reference field="7" count="1" selected="0" defaultSubtotal="1">
             <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="32">
-      <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -6019,6 +6005,15 @@
       </pivotArea>
     </format>
     <format dxfId="29">
+      <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -6027,7 +6022,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -6050,7 +6045,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:D22" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -6673,7 +6668,7 @@
     <dataField name="Suma de Cantidad" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="27">
+    <format dxfId="26">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4" count="0" selected="0"/>
@@ -6693,7 +6688,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="25">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1" selected="0">
@@ -6702,7 +6697,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="24">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4" count="1" selected="0">
@@ -6734,7 +6729,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:G22" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -7432,7 +7427,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="24">
+    <format dxfId="23">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -7441,7 +7436,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="22">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -7464,7 +7459,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:G71" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -8299,7 +8294,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="22">
+    <format dxfId="21">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -8311,7 +8306,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="20">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -8319,15 +8314,6 @@
           </reference>
           <reference field="7" count="1" selected="0" defaultSubtotal="1">
             <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="20">
-      <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -8351,6 +8337,15 @@
       </pivotArea>
     </format>
     <format dxfId="17">
+      <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="16">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8359,7 +8354,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8382,7 +8377,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:E54" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -9156,15 +9151,6 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="15">
-      <pivotArea field="7" grandRow="1" outline="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
     <format dxfId="14">
       <pivotArea field="7" grandRow="1" outline="0">
         <references count="1">
@@ -9184,6 +9170,15 @@
       </pivotArea>
     </format>
     <format dxfId="12">
+      <pivotArea field="7" grandRow="1" outline="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="11">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -9192,7 +9187,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -9215,7 +9210,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -9901,33 +9896,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}" name="Tabla1" displayName="Tabla1" ref="A9:S120" totalsRowShown="0" headerRowDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}" name="Tabla1" displayName="Tabla1" ref="A9:S120" totalsRowShown="0" headerRowDxfId="45">
   <autoFilter ref="A9:S120" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:S119">
     <sortCondition ref="O9:O119"/>
   </sortState>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{ABC9D6B9-B435-44A8-AC1D-3A7F3684B351}" name="Solicita"/>
-    <tableColumn id="2" xr3:uid="{D6EB60C5-1C40-47ED-9FB1-374E19B24E9A}" name="Fecha" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{D6EB60C5-1C40-47ED-9FB1-374E19B24E9A}" name="Fecha" dataDxfId="44"/>
     <tableColumn id="3" xr3:uid="{D0A4671C-530D-455C-9B7A-52F52FA87E23}" name="Rubro"/>
     <tableColumn id="4" xr3:uid="{E2744C88-A32D-477A-A488-E2EEDE9A0D41}" name="Cantidad"/>
     <tableColumn id="5" xr3:uid="{681C651D-E929-4B0E-B5D7-68CE0CD4311A}" name="U/M"/>
     <tableColumn id="6" xr3:uid="{FD6A41E2-5215-422B-AB72-C8073C73180D}" name="Articulo"/>
     <tableColumn id="7" xr3:uid="{D3D27FF5-A21A-484B-8256-6DC392426D15}" name="Proveedor"/>
     <tableColumn id="8" xr3:uid="{B7EE972F-E2DD-462D-A500-A25FF2470135}" name="Sector"/>
-    <tableColumn id="9" xr3:uid="{02FC2EEA-023E-4B2F-B485-DC353A71EC23}" name="Moneda" dataDxfId="44">
+    <tableColumn id="9" xr3:uid="{02FC2EEA-023E-4B2F-B485-DC353A71EC23}" name="Moneda" dataDxfId="43">
       <calculatedColumnFormula>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[[Descripcion]:[Moneda]],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{DD121184-680A-4A3A-BF4B-A9D24FF92624}" name="$" dataCellStyle="Moneda">
       <calculatedColumnFormula>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{1E29690A-AD00-49F3-AB46-FD0AF8DCE7AE}" name="Importe" dataDxfId="43" dataCellStyle="Moneda">
+    <tableColumn id="18" xr3:uid="{1E29690A-AD00-49F3-AB46-FD0AF8DCE7AE}" name="Importe" dataDxfId="42" dataCellStyle="Moneda">
       <calculatedColumnFormula>IF(I10="$", J10/$H$1, IF(I10="U$D", J10*1, 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{0C4F4870-64EC-4168-97BE-8674B96B82BB}" name="Total" dataDxfId="42" dataCellStyle="Moneda">
+    <tableColumn id="19" xr3:uid="{0C4F4870-64EC-4168-97BE-8674B96B82BB}" name="Total" dataDxfId="41" dataCellStyle="Moneda">
       <calculatedColumnFormula>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2EA38B46-DCBE-4340-A2A4-DD6B043C95F4}" name="Fecha Entrega" dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{2EA38B46-DCBE-4340-A2A4-DD6B043C95F4}" name="Fecha Entrega" dataDxfId="40"/>
     <tableColumn id="12" xr3:uid="{4DC2766A-D25F-4018-B804-F35119E17C75}" name="Mes">
       <calculatedColumnFormula>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</calculatedColumnFormula>
     </tableColumn>
@@ -9942,31 +9937,31 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BF6A21D0-BF74-405C-816D-FF180DA65A53}" name="Tabla2" displayName="Tabla2" ref="A2:D18" totalsRowShown="0" headerRowDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BF6A21D0-BF74-405C-816D-FF180DA65A53}" name="Tabla2" displayName="Tabla2" ref="A2:D18" totalsRowShown="0" headerRowDxfId="39">
   <autoFilter ref="A2:D18" xr:uid="{BF6A21D0-BF74-405C-816D-FF180DA65A53}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4C9ED8A6-DE10-4FC9-A1A8-C9C31853D309}" name="Descripcion" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{4C9ED8A6-DE10-4FC9-A1A8-C9C31853D309}" name="Descripcion" dataDxfId="38"/>
     <tableColumn id="2" xr3:uid="{17F4999B-AFFB-423F-81FC-E94D2D51FCC4}" name="U/M"/>
     <tableColumn id="4" xr3:uid="{AED66179-0481-4D19-8718-F67F09D2A74F}" name="Moneda"/>
-    <tableColumn id="3" xr3:uid="{8D449BA5-7410-4173-AB96-0B1F4A36CC9F}" name="$" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{8D449BA5-7410-4173-AB96-0B1F4A36CC9F}" name="$" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EB8C7E4-857A-45C7-8640-F7ED83B0E987}" name="Tabla3" displayName="Tabla3" ref="B2:H15" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EB8C7E4-857A-45C7-8640-F7ED83B0E987}" name="Tabla3" displayName="Tabla3" ref="B2:H15" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="B2:H15" xr:uid="{8EB8C7E4-857A-45C7-8640-F7ED83B0E987}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{48393E8F-75FE-4E2C-B5A6-0DA171776A4D}" name="Fecha" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{963F1D5B-BEA1-44D4-93E6-186C3DBEAC18}" name="Tipo" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{193244C5-51AA-4CBE-9C5C-987B16E24CCC}" name="Comprobante" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{8FFB7E5E-DF58-448C-A2B8-F8E260D7153A}" name="TN" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{87858EB0-F199-426F-9BD2-3508F9DACC9D}" name="$" dataDxfId="4" dataCellStyle="Moneda"/>
-    <tableColumn id="5" xr3:uid="{DC37D9EF-761A-4BBE-A4AB-069249B5CE73}" name="$Total" dataDxfId="3" dataCellStyle="Moneda">
+    <tableColumn id="1" xr3:uid="{48393E8F-75FE-4E2C-B5A6-0DA171776A4D}" name="Fecha" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{963F1D5B-BEA1-44D4-93E6-186C3DBEAC18}" name="Tipo" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{193244C5-51AA-4CBE-9C5C-987B16E24CCC}" name="Comprobante" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{8FFB7E5E-DF58-448C-A2B8-F8E260D7153A}" name="TN" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{87858EB0-F199-426F-9BD2-3508F9DACC9D}" name="$" dataDxfId="3" dataCellStyle="Moneda"/>
+    <tableColumn id="5" xr3:uid="{DC37D9EF-761A-4BBE-A4AB-069249B5CE73}" name="$Total" dataDxfId="2" dataCellStyle="Moneda">
       <calculatedColumnFormula>F3*E3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{66202679-348D-4EC3-8EBB-E8E14B182F31}" name="$IVA" dataDxfId="2" dataCellStyle="Moneda">
+    <tableColumn id="6" xr3:uid="{66202679-348D-4EC3-8EBB-E8E14B182F31}" name="$IVA" dataDxfId="1" dataCellStyle="Moneda">
       <calculatedColumnFormula>G3*1.21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10323,7 +10318,7 @@
         <v>164</v>
       </c>
       <c r="H1" s="8">
-        <v>1520</v>
+        <v>1535</v>
       </c>
       <c r="I1" s="2"/>
     </row>
@@ -10348,15 +10343,15 @@
       </c>
       <c r="K3" s="27">
         <f>SUM(L3:M3)</f>
-        <v>316296.13157894742</v>
+        <v>315339.51140065148</v>
       </c>
       <c r="L3" s="28">
         <f>SUMIFS(L:L, H:H, "INSUMOS DE CAMPAÑA", O:O, "Cumplido")</f>
-        <v>316092.13157894742</v>
+        <v>315339.51140065148</v>
       </c>
       <c r="M3" s="29">
         <f>SUMIFS(L:L, H:H, "INSUMOS DE CAMPAÑA", O:O, "Pendiente")</f>
-        <v>204.00000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -10387,15 +10382,15 @@
       </c>
       <c r="K6" s="34">
         <f>SUM(K3:K5)</f>
-        <v>435519.16337894741</v>
+        <v>434562.54320065147</v>
       </c>
       <c r="L6" s="34">
         <f>SUM(L3:L5)</f>
-        <v>368748.6433789474</v>
+        <v>367996.02320065146</v>
       </c>
       <c r="M6" s="35">
         <f>SUM(M3:M5)</f>
-        <v>66770.52</v>
+        <v>66566.52</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -10404,15 +10399,15 @@
       </c>
       <c r="K7" s="36">
         <f>K6*H1</f>
-        <v>661989128.33600008</v>
+        <v>667053503.81299996</v>
       </c>
       <c r="L7" s="36">
         <f>L6*H1</f>
-        <v>560497937.93599999</v>
+        <v>564873895.61300004</v>
       </c>
       <c r="M7" s="37">
         <f>M6*H1</f>
-        <v>101491190.40000001</v>
+        <v>102179608.2</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12265,11 +12260,11 @@
       </c>
       <c r="K41" s="2">
         <f t="shared" si="0"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L41" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2394.0986842105262</v>
+        <v>2370.7035830618893</v>
       </c>
       <c r="M41" s="1">
         <v>46037</v>
@@ -12323,11 +12318,11 @@
       </c>
       <c r="K42" s="2">
         <f t="shared" ref="K42:K73" si="1">IF(I42="$", J42/$H$1, IF(I42="U$D", J42*1, 0))</f>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L42" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2394.0986842105262</v>
+        <v>2370.7035830618893</v>
       </c>
       <c r="M42" s="1">
         <v>46037</v>
@@ -12381,11 +12376,11 @@
       </c>
       <c r="K43" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L43" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2443.9342105263158</v>
+        <v>2420.0521172638437</v>
       </c>
       <c r="M43" s="1">
         <v>46063</v>
@@ -12439,11 +12434,11 @@
       </c>
       <c r="K44" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L44" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2443.9342105263158</v>
+        <v>2420.0521172638437</v>
       </c>
       <c r="M44" s="1">
         <v>46066</v>
@@ -12497,11 +12492,11 @@
       </c>
       <c r="K45" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L45" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1763.5131578947367</v>
+        <v>1746.2801302931596</v>
       </c>
       <c r="M45" s="1">
         <v>46070</v>
@@ -12555,11 +12550,11 @@
       </c>
       <c r="K46" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L46" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2206.0526315789475</v>
+        <v>2184.495114006515</v>
       </c>
       <c r="M46" s="1">
         <v>46073</v>
@@ -12613,11 +12608,11 @@
       </c>
       <c r="K47" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L47" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2272.5</v>
+        <v>2250.2931596091207</v>
       </c>
       <c r="M47" s="1">
         <v>46077</v>
@@ -12671,11 +12666,11 @@
       </c>
       <c r="K48" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L48" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2384.1315789473683</v>
+        <v>2360.8338762214985</v>
       </c>
       <c r="M48" s="1">
         <v>46080</v>
@@ -12729,11 +12724,11 @@
       </c>
       <c r="K49" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L49" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2279.144736842105</v>
+        <v>2256.8729641693812</v>
       </c>
       <c r="M49" s="1">
         <v>46085</v>
@@ -12787,11 +12782,11 @@
       </c>
       <c r="K50" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L50" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2611.3815789473683</v>
+        <v>2585.8631921824103</v>
       </c>
       <c r="M50" s="1">
         <v>46087</v>
@@ -12845,11 +12840,11 @@
       </c>
       <c r="K51" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L51" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1857.8684210526317</v>
+        <v>1839.7133550488602</v>
       </c>
       <c r="M51" s="1">
         <v>46094</v>
@@ -12903,11 +12898,11 @@
       </c>
       <c r="K52" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L52" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2031.9605263157894</v>
+        <v>2012.1042345276874</v>
       </c>
       <c r="M52" s="1">
         <v>46095</v>
@@ -12961,11 +12956,11 @@
       </c>
       <c r="K53" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L53" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2101.0657894736842</v>
+        <v>2080.5342019543978</v>
       </c>
       <c r="M53" s="1">
         <v>46098</v>
@@ -13022,11 +13017,11 @@
       </c>
       <c r="K54" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L54" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1860.5263157894738</v>
+        <v>1842.3452768729644</v>
       </c>
       <c r="M54" s="1">
         <v>46103</v>
@@ -13083,11 +13078,11 @@
       </c>
       <c r="K55" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L55" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2522.3421052631579</v>
+        <v>2497.6938110749188</v>
       </c>
       <c r="M55" s="1">
         <v>46106</v>
@@ -13144,11 +13139,11 @@
       </c>
       <c r="K56" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L56" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2004.0526315789473</v>
+        <v>1984.4690553745929</v>
       </c>
       <c r="M56" s="1">
         <v>46108</v>
@@ -13205,11 +13200,11 @@
       </c>
       <c r="K57" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L57" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2095.75</v>
+        <v>2075.2703583061889</v>
       </c>
       <c r="M57" s="1">
         <v>46107</v>
@@ -13266,11 +13261,11 @@
       </c>
       <c r="K58" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L58" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2354.894736842105</v>
+        <v>2331.8827361563517</v>
       </c>
       <c r="M58" s="1">
         <v>46111</v>
@@ -13327,11 +13322,11 @@
       </c>
       <c r="K59" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L59" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2265.8552631578946</v>
+        <v>2243.7133550488602</v>
       </c>
       <c r="M59" s="1">
         <v>46112</v>
@@ -13388,11 +13383,11 @@
       </c>
       <c r="K60" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L60" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2416.0263157894738</v>
+        <v>2392.4169381107495</v>
       </c>
       <c r="M60" s="1">
         <v>46113</v>
@@ -13449,11 +13444,11 @@
       </c>
       <c r="K61" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L61" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1993.421052631579</v>
+        <v>1973.9413680781761</v>
       </c>
       <c r="M61" s="1">
         <v>46118</v>
@@ -13510,11 +13505,11 @@
       </c>
       <c r="K62" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L62" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2455.8947368421054</v>
+        <v>2431.8957654723131</v>
       </c>
       <c r="M62" s="1">
         <v>46120</v>
@@ -13571,11 +13566,11 @@
       </c>
       <c r="K63" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L63" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2154.2236842105262</v>
+        <v>2133.1726384364824</v>
       </c>
       <c r="M63" s="1">
         <v>46121</v>
@@ -13632,11 +13627,11 @@
       </c>
       <c r="K64" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L64" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2244.5921052631579</v>
+        <v>2222.6579804560265</v>
       </c>
       <c r="M64" s="1">
         <v>46125</v>
@@ -13693,11 +13688,11 @@
       </c>
       <c r="K65" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L65" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2006.7105263157894</v>
+        <v>1987.1009771986971</v>
       </c>
       <c r="M65" s="1">
         <v>46127</v>
@@ -13754,11 +13749,11 @@
       </c>
       <c r="K66" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L66" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2147.5789473684208</v>
+        <v>2126.5928338762214</v>
       </c>
       <c r="M66" s="1">
         <v>46129</v>
@@ -13815,11 +13810,11 @@
       </c>
       <c r="K67" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L67" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2130.3026315789475</v>
+        <v>2109.4853420195441</v>
       </c>
       <c r="M67" s="1">
         <v>46143</v>
@@ -13876,11 +13871,11 @@
       </c>
       <c r="K68" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L68" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1988.1052631578948</v>
+        <v>1968.6775244299677</v>
       </c>
       <c r="M68" s="1">
         <v>46147</v>
@@ -13937,11 +13932,11 @@
       </c>
       <c r="K69" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L69" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1869.828947368421</v>
+        <v>1851.5570032573291</v>
       </c>
       <c r="M69" s="1">
         <v>46134</v>
@@ -13998,11 +13993,11 @@
       </c>
       <c r="K70" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L70" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1913.6842105263158</v>
+        <v>1894.9837133550491</v>
       </c>
       <c r="M70" s="1">
         <v>46136</v>
@@ -14059,11 +14054,11 @@
       </c>
       <c r="K71" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L71" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1950.8947368421052</v>
+        <v>1931.8306188925083</v>
       </c>
       <c r="M71" s="1">
         <v>46157</v>
@@ -14120,11 +14115,11 @@
       </c>
       <c r="K72" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L72" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1970.828947368421</v>
+        <v>1951.5700325732901</v>
       </c>
       <c r="M72" s="1">
         <v>46161</v>
@@ -14181,11 +14176,11 @@
       </c>
       <c r="K73" s="2">
         <f t="shared" si="1"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L73" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2079.8026315789475</v>
+        <v>2059.4788273615636</v>
       </c>
       <c r="M73" s="1">
         <v>46164</v>
@@ -14242,11 +14237,11 @@
       </c>
       <c r="K74" s="2">
         <f t="shared" ref="K74:K105" si="2">IF(I74="$", J74/$H$1, IF(I74="U$D", J74*1, 0))</f>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L74" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1885.7763157894735</v>
+        <v>1867.3485342019544</v>
       </c>
       <c r="M74" s="1">
         <v>46150</v>
@@ -14297,11 +14292,11 @@
       </c>
       <c r="K75" s="2">
         <f t="shared" si="2"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L75" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2134.2894736842104</v>
+        <v>2113.4332247557004</v>
       </c>
       <c r="M75" s="1">
         <v>46162</v>
@@ -14352,11 +14347,11 @@
       </c>
       <c r="K76" s="2">
         <f t="shared" si="2"/>
-        <v>66.44736842105263</v>
+        <v>65.798045602605868</v>
       </c>
       <c r="L76" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1969.5</v>
+        <v>1950.254071661238</v>
       </c>
       <c r="M76" s="1">
         <v>46185</v>
@@ -14407,11 +14402,11 @@
       </c>
       <c r="K77" s="2">
         <f t="shared" si="2"/>
-        <v>90.46052631578948</v>
+        <v>89.576547231270354</v>
       </c>
       <c r="L77" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2605.2631578947371</v>
+        <v>2579.8045602605862</v>
       </c>
       <c r="M77" s="1">
         <v>46069</v>
@@ -14465,11 +14460,11 @@
       </c>
       <c r="K78" s="2">
         <f t="shared" si="2"/>
-        <v>90.46052631578948</v>
+        <v>89.576547231270354</v>
       </c>
       <c r="L78" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2558.2236842105267</v>
+        <v>2533.2247557003257</v>
       </c>
       <c r="M78" s="1">
         <v>46081</v>
@@ -14523,11 +14518,11 @@
       </c>
       <c r="K79" s="2">
         <f t="shared" si="2"/>
-        <v>90.46052631578948</v>
+        <v>89.576547231270354</v>
       </c>
       <c r="L79" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2605.2631578947371</v>
+        <v>2579.8045602605862</v>
       </c>
       <c r="M79" s="1">
         <v>46088</v>
@@ -14581,11 +14576,11 @@
       </c>
       <c r="K80" s="2">
         <f t="shared" si="2"/>
-        <v>90.46052631578948</v>
+        <v>89.576547231270354</v>
       </c>
       <c r="L80" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2605.2631578947371</v>
+        <v>2579.8045602605862</v>
       </c>
       <c r="M80" s="1">
         <v>46101</v>
@@ -14642,11 +14637,11 @@
       </c>
       <c r="K81" s="2">
         <f t="shared" si="2"/>
-        <v>90.46052631578948</v>
+        <v>89.576547231270354</v>
       </c>
       <c r="L81" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2532.8947368421054</v>
+        <v>2508.1433224755701</v>
       </c>
       <c r="M81" s="1">
         <v>46114</v>
@@ -14700,11 +14695,11 @@
       </c>
       <c r="K82" s="2">
         <f t="shared" si="2"/>
-        <v>90.46052631578948</v>
+        <v>89.576547231270354</v>
       </c>
       <c r="L82" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2496.7105263157896</v>
+        <v>2472.3127035830621</v>
       </c>
       <c r="M82" s="1">
         <v>46129</v>
@@ -14761,11 +14756,11 @@
       </c>
       <c r="K83" s="2">
         <f t="shared" si="2"/>
-        <v>90.46052631578948</v>
+        <v>89.576547231270354</v>
       </c>
       <c r="L83" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1338.8157894736844</v>
+        <v>1325.7328990228013</v>
       </c>
       <c r="M83" s="1">
         <v>46153</v>
@@ -14816,11 +14811,11 @@
       </c>
       <c r="K84" s="2">
         <f t="shared" si="2"/>
-        <v>101.97368421052632</v>
+        <v>100.9771986970684</v>
       </c>
       <c r="L84" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1509.2105263157896</v>
+        <v>1494.4625407166125</v>
       </c>
       <c r="M84" s="1">
         <v>46153</v>
@@ -16229,6 +16224,9 @@
       <c r="F109" t="s">
         <v>26</v>
       </c>
+      <c r="G109" t="s">
+        <v>90</v>
+      </c>
       <c r="H109" t="s">
         <v>83</v>
       </c>
@@ -16256,7 +16254,10 @@
         <v>mayo</v>
       </c>
       <c r="O109" t="s">
-        <v>24</v>
+        <v>31</v>
+      </c>
+      <c r="P109" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
@@ -16824,13 +16825,13 @@
         <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</f>
         <v>101000</v>
       </c>
-      <c r="K120" s="43">
+      <c r="K120" s="2">
         <f>IF(I120="$", J120/$H$1, IF(I120="U$D", J120*1, 0))</f>
-        <v>66.44736842105263</v>
-      </c>
-      <c r="L120" s="43">
+        <v>65.798045602605868</v>
+      </c>
+      <c r="L120" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2043.921052631579</v>
+        <v>2023.9478827361565</v>
       </c>
       <c r="M120" s="1">
         <v>46254</v>
@@ -16848,7 +16849,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A10:P120">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$O10="cumplido"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/public/data/pedido quimicos campaña 2026 valorizado.xlsx
+++ b/public/data/pedido quimicos campaña 2026 valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fincalaseis-my.sharepoint.com/personal/compras_fincalaseis_com_ar/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2172" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB6E2232-167E-49E7-993A-517E836BBF11}"/>
+  <xr:revisionPtr revIDLastSave="2191" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{582D91A9-F974-4631-A89E-9810F01314D0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8EF26D9B-9BDD-40EA-9926-EAD75B18C35F}"/>
   </bookViews>
@@ -32,7 +32,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId13"/>
+    <pivotCache cacheId="8" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="190">
   <si>
     <t>Solicita</t>
   </si>
@@ -631,6 +631,9 @@
   <si>
     <t>septiembre</t>
   </si>
+  <si>
+    <t>R-1-577</t>
+  </si>
 </sst>
 </file>
 
@@ -865,7 +868,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -942,187 +945,17 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 3" xfId="2" xr:uid="{1D32B0D1-24D0-4CD1-BA07-AB849F504D40}"/>
   </cellStyles>
-  <dxfs count="80">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4" tint="0.79998168889431442"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$USD]\ * #,##0.00_-;\-[$USD]\ * #,##0.00_-;_-[$USD]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$USD]\ * #,##0.00_-;\-[$USD]\ * #,##0.00_-;_-[$USD]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4" tint="0.79998168889431442"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$USD]\ * #,##0.00_-;\-[$USD]\ * #,##0.00_-;_-[$USD]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$USD]\ * #,##0.00_-;\-[$USD]\ * #,##0.00_-;_-[$USD]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4" tint="0.79998168889431442"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4" tint="0.79998168889431442"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$USD]\ * #,##0.00_-;\-[$USD]\ * #,##0.00_-;_-[$USD]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$USD]\ * #,##0.00_-;\-[$USD]\ * #,##0.00_-;_-[$USD]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4" tint="0.79998168889431442"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$USD]\ * #,##0.00_-;\-[$USD]\ * #,##0.00_-;_-[$USD]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$USD]\ * #,##0.00_-;\-[$USD]\ * #,##0.00_-;_-[$USD]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
+  <dxfs count="46">
     <dxf>
       <fill>
         <patternFill>
@@ -1440,22 +1273,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>575275</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>179184</xdr:rowOff>
+      <xdr:colOff>561951</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1065671</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>182517</xdr:rowOff>
+      <xdr:colOff>1087951</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>9431</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 3">
+        <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E31B4A5D-0DEF-4A6A-6DC3-36E830FE7551}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B82B9736-1973-2A46-643C-798242246E85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1471,8 +1304,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6554334" y="179184"/>
-          <a:ext cx="2093614" cy="1182170"/>
+          <a:off x="6541010" y="198044"/>
+          <a:ext cx="2129218" cy="1178837"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4689,7 +4522,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:F4" firstHeaderRow="0" firstDataRow="1" firstDataCol="4"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5259,7 +5092,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="70">
+    <format dxfId="36">
       <pivotArea outline="0" fieldPosition="0">
         <references count="5">
           <reference field="4294967294" count="1" selected="0">
@@ -5278,7 +5111,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="35">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5291,7 +5124,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="68">
+    <format dxfId="34">
       <pivotArea outline="0" fieldPosition="0">
         <references count="5">
           <reference field="4294967294" count="1" selected="0">
@@ -5331,7 +5164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:E12" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5935,7 +5768,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="67">
+    <format dxfId="33">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5947,7 +5780,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="32">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5959,7 +5792,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="65">
+    <format dxfId="31">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5968,7 +5801,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="30">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5977,7 +5810,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="29">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5986,7 +5819,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="62">
+    <format dxfId="28">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5995,7 +5828,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -6018,7 +5851,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:D22" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -6644,7 +6477,7 @@
     <dataField name="Suma de Cantidad" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="60">
+    <format dxfId="26">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4" count="0" selected="0"/>
@@ -6664,7 +6497,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="59">
+    <format dxfId="25">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1" selected="0">
@@ -6673,7 +6506,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="58">
+    <format dxfId="24">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4" count="1" selected="0">
@@ -6705,7 +6538,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:G22" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -7406,7 +7239,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="57">
+    <format dxfId="23">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -7415,7 +7248,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="22">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -7438,7 +7271,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:G66" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -8258,7 +8091,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="55">
+    <format dxfId="21">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -8270,7 +8103,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="54">
+    <format dxfId="20">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -8282,7 +8115,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="19">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8291,7 +8124,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="18">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8300,7 +8133,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="17">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8309,7 +8142,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="50">
+    <format dxfId="16">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8318,7 +8151,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="49">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8341,7 +8174,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:E63" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -9156,7 +8989,7 @@
     <dataField name="Suma de Total" fld="11" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="48">
+    <format dxfId="14">
       <pivotArea field="7" grandRow="1" outline="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -9165,7 +8998,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="13">
       <pivotArea field="7" grandRow="1" outline="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -9174,7 +9007,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="46">
+    <format dxfId="12">
       <pivotArea field="7" grandRow="1" outline="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -9183,7 +9016,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="45">
+    <format dxfId="11">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -9192,7 +9025,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -9215,7 +9048,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -9895,33 +9728,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}" name="Tabla1" displayName="Tabla1" ref="A9:S113" totalsRowShown="0" headerRowDxfId="79">
-  <autoFilter ref="A9:S113" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:S112">
-    <sortCondition ref="O9:O112"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}" name="Tabla1" displayName="Tabla1" ref="A9:S114" totalsRowShown="0" headerRowDxfId="45">
+  <autoFilter ref="A9:S114" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:S113">
+    <sortCondition ref="O9:O113"/>
   </sortState>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{ABC9D6B9-B435-44A8-AC1D-3A7F3684B351}" name="Solicita"/>
-    <tableColumn id="2" xr3:uid="{D6EB60C5-1C40-47ED-9FB1-374E19B24E9A}" name="Fecha" dataDxfId="78"/>
+    <tableColumn id="2" xr3:uid="{D6EB60C5-1C40-47ED-9FB1-374E19B24E9A}" name="Fecha" dataDxfId="44"/>
     <tableColumn id="3" xr3:uid="{D0A4671C-530D-455C-9B7A-52F52FA87E23}" name="Rubro"/>
     <tableColumn id="4" xr3:uid="{E2744C88-A32D-477A-A488-E2EEDE9A0D41}" name="Cantidad"/>
     <tableColumn id="5" xr3:uid="{681C651D-E929-4B0E-B5D7-68CE0CD4311A}" name="U/M"/>
     <tableColumn id="6" xr3:uid="{FD6A41E2-5215-422B-AB72-C8073C73180D}" name="Articulo"/>
     <tableColumn id="7" xr3:uid="{D3D27FF5-A21A-484B-8256-6DC392426D15}" name="Proveedor"/>
     <tableColumn id="8" xr3:uid="{B7EE972F-E2DD-462D-A500-A25FF2470135}" name="Sector"/>
-    <tableColumn id="9" xr3:uid="{02FC2EEA-023E-4B2F-B485-DC353A71EC23}" name="Moneda" dataDxfId="77">
+    <tableColumn id="9" xr3:uid="{02FC2EEA-023E-4B2F-B485-DC353A71EC23}" name="Moneda" dataDxfId="43">
       <calculatedColumnFormula>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[[Descripcion]:[Moneda]],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{DD121184-680A-4A3A-BF4B-A9D24FF92624}" name="$" dataCellStyle="Moneda">
       <calculatedColumnFormula>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{1E29690A-AD00-49F3-AB46-FD0AF8DCE7AE}" name="Importe" dataDxfId="76" dataCellStyle="Moneda">
+    <tableColumn id="18" xr3:uid="{1E29690A-AD00-49F3-AB46-FD0AF8DCE7AE}" name="Importe" dataDxfId="42" dataCellStyle="Moneda">
       <calculatedColumnFormula>IF(I10="$", J10/$H$1, IF(I10="U$D", J10*1, 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{0C4F4870-64EC-4168-97BE-8674B96B82BB}" name="Total" dataDxfId="75" dataCellStyle="Moneda">
+    <tableColumn id="19" xr3:uid="{0C4F4870-64EC-4168-97BE-8674B96B82BB}" name="Total" dataDxfId="41" dataCellStyle="Moneda">
       <calculatedColumnFormula>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2EA38B46-DCBE-4340-A2A4-DD6B043C95F4}" name="Fecha Entrega" dataDxfId="74"/>
+    <tableColumn id="11" xr3:uid="{2EA38B46-DCBE-4340-A2A4-DD6B043C95F4}" name="Fecha Entrega" dataDxfId="40"/>
     <tableColumn id="12" xr3:uid="{4DC2766A-D25F-4018-B804-F35119E17C75}" name="Mes">
       <calculatedColumnFormula>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</calculatedColumnFormula>
     </tableColumn>
@@ -9936,31 +9769,31 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BF6A21D0-BF74-405C-816D-FF180DA65A53}" name="Tabla2" displayName="Tabla2" ref="A2:D18" totalsRowShown="0" headerRowDxfId="73">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BF6A21D0-BF74-405C-816D-FF180DA65A53}" name="Tabla2" displayName="Tabla2" ref="A2:D18" totalsRowShown="0" headerRowDxfId="39">
   <autoFilter ref="A2:D18" xr:uid="{BF6A21D0-BF74-405C-816D-FF180DA65A53}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4C9ED8A6-DE10-4FC9-A1A8-C9C31853D309}" name="Descripcion" dataDxfId="72"/>
+    <tableColumn id="1" xr3:uid="{4C9ED8A6-DE10-4FC9-A1A8-C9C31853D309}" name="Descripcion" dataDxfId="38"/>
     <tableColumn id="2" xr3:uid="{17F4999B-AFFB-423F-81FC-E94D2D51FCC4}" name="U/M"/>
     <tableColumn id="4" xr3:uid="{AED66179-0481-4D19-8718-F67F09D2A74F}" name="Moneda"/>
-    <tableColumn id="3" xr3:uid="{8D449BA5-7410-4173-AB96-0B1F4A36CC9F}" name="$" dataDxfId="71"/>
+    <tableColumn id="3" xr3:uid="{8D449BA5-7410-4173-AB96-0B1F4A36CC9F}" name="$" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EB8C7E4-857A-45C7-8640-F7ED83B0E987}" name="Tabla3" displayName="Tabla3" ref="B2:H15" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EB8C7E4-857A-45C7-8640-F7ED83B0E987}" name="Tabla3" displayName="Tabla3" ref="B2:H15" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="B2:H15" xr:uid="{8EB8C7E4-857A-45C7-8640-F7ED83B0E987}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{48393E8F-75FE-4E2C-B5A6-0DA171776A4D}" name="Fecha" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{963F1D5B-BEA1-44D4-93E6-186C3DBEAC18}" name="Tipo" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{193244C5-51AA-4CBE-9C5C-987B16E24CCC}" name="Comprobante" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{8FFB7E5E-DF58-448C-A2B8-F8E260D7153A}" name="TN" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{87858EB0-F199-426F-9BD2-3508F9DACC9D}" name="$" dataDxfId="37" dataCellStyle="Moneda"/>
-    <tableColumn id="5" xr3:uid="{DC37D9EF-761A-4BBE-A4AB-069249B5CE73}" name="$Total" dataDxfId="36" dataCellStyle="Moneda">
+    <tableColumn id="1" xr3:uid="{48393E8F-75FE-4E2C-B5A6-0DA171776A4D}" name="Fecha" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{963F1D5B-BEA1-44D4-93E6-186C3DBEAC18}" name="Tipo" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{193244C5-51AA-4CBE-9C5C-987B16E24CCC}" name="Comprobante" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{8FFB7E5E-DF58-448C-A2B8-F8E260D7153A}" name="TN" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{87858EB0-F199-426F-9BD2-3508F9DACC9D}" name="$" dataDxfId="3" dataCellStyle="Moneda"/>
+    <tableColumn id="5" xr3:uid="{DC37D9EF-761A-4BBE-A4AB-069249B5CE73}" name="$Total" dataDxfId="2" dataCellStyle="Moneda">
       <calculatedColumnFormula>F3*E3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{66202679-348D-4EC3-8EBB-E8E14B182F31}" name="$IVA" dataDxfId="35" dataCellStyle="Moneda">
+    <tableColumn id="6" xr3:uid="{66202679-348D-4EC3-8EBB-E8E14B182F31}" name="$IVA" dataDxfId="1" dataCellStyle="Moneda">
       <calculatedColumnFormula>G3*1.21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10289,7 +10122,7 @@
     <tabColor theme="6"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S113"/>
+  <dimension ref="A1:S114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -10317,7 +10150,7 @@
         <v>159</v>
       </c>
       <c r="H1" s="8">
-        <v>1535</v>
+        <v>1545</v>
       </c>
       <c r="I1" s="2"/>
     </row>
@@ -10342,15 +10175,15 @@
       </c>
       <c r="K3" s="27">
         <f>SUM(L3:M3)</f>
-        <v>315509.51140065148</v>
+        <v>314882.08414239483</v>
       </c>
       <c r="L3" s="28">
         <f>SUMIFS(L:L, H:H, "INSUMOS DE CAMPAÑA", O:O, "Cumplido")</f>
-        <v>315339.51140065148</v>
+        <v>314882.08414239483</v>
       </c>
       <c r="M3" s="29">
         <f>SUMIFS(L:L, H:H, "INSUMOS DE CAMPAÑA", O:O, "Pendiente")</f>
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -10363,11 +10196,11 @@
       </c>
       <c r="L4" s="31">
         <f>SUMIFS(L:L, H:H, "PRODUCCION DE PASTA", O:O, "Cumplido")</f>
-        <v>52656.511799999986</v>
+        <v>53506.511799999986</v>
       </c>
       <c r="M4" s="32">
         <f>SUMIFS(L:L, H:H, "PRODUCCION DE PASTA", O:O, "Pendiente")</f>
-        <v>4665.7</v>
+        <v>3815.7</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10381,15 +10214,15 @@
       </c>
       <c r="K6" s="34">
         <f>SUM(K3:K5)</f>
-        <v>372831.72320065147</v>
+        <v>372204.29594239482</v>
       </c>
       <c r="L6" s="34">
         <f>SUM(L3:L5)</f>
-        <v>367996.02320065146</v>
+        <v>368388.59594239481</v>
       </c>
       <c r="M6" s="35">
         <f>SUM(M3:M5)</f>
-        <v>4835.7</v>
+        <v>3815.7</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -10398,15 +10231,15 @@
       </c>
       <c r="K7" s="36">
         <f>K6*H1</f>
-        <v>572296695.11300004</v>
+        <v>575055637.23099995</v>
       </c>
       <c r="L7" s="36">
         <f>L6*H1</f>
-        <v>564873895.61300004</v>
+        <v>569160380.73099995</v>
       </c>
       <c r="M7" s="37">
         <f>M6*H1</f>
-        <v>7422799.5</v>
+        <v>5895256.5</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11524,23 +11357,26 @@
         <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</f>
         <v>0.34</v>
       </c>
-      <c r="K28" s="40">
+      <c r="K28" s="2">
         <f>IF(I28="$", J28/$H$1, IF(I28="U$D", J28*1, 0))</f>
         <v>0.34</v>
       </c>
-      <c r="L28" s="40">
+      <c r="L28" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
         <v>170</v>
       </c>
       <c r="M28" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="N28" t="str">
         <f>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</f>
         <v>septiembre</v>
       </c>
       <c r="O28" t="s">
-        <v>24</v>
+        <v>31</v>
+      </c>
+      <c r="P28" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -12311,11 +12147,11 @@
       </c>
       <c r="K42" s="2">
         <f t="shared" si="0"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L42" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2370.7035830618893</v>
+        <v>2355.3592233009708</v>
       </c>
       <c r="M42" s="1">
         <v>46037</v>
@@ -12369,11 +12205,11 @@
       </c>
       <c r="K43" s="2">
         <f t="shared" ref="K43:K74" si="1">IF(I43="$", J43/$H$1, IF(I43="U$D", J43*1, 0))</f>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L43" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2370.7035830618893</v>
+        <v>2355.3592233009708</v>
       </c>
       <c r="M43" s="1">
         <v>46037</v>
@@ -12427,11 +12263,11 @@
       </c>
       <c r="K44" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L44" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2420.0521172638437</v>
+        <v>2404.3883495145628</v>
       </c>
       <c r="M44" s="1">
         <v>46063</v>
@@ -12485,11 +12321,11 @@
       </c>
       <c r="K45" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L45" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2420.0521172638437</v>
+        <v>2404.3883495145628</v>
       </c>
       <c r="M45" s="1">
         <v>46066</v>
@@ -12543,11 +12379,11 @@
       </c>
       <c r="K46" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L46" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1746.2801302931596</v>
+        <v>1734.9773462783169</v>
       </c>
       <c r="M46" s="1">
         <v>46070</v>
@@ -12601,11 +12437,11 @@
       </c>
       <c r="K47" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L47" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2184.495114006515</v>
+        <v>2170.3559870550162</v>
       </c>
       <c r="M47" s="1">
         <v>46073</v>
@@ -12659,11 +12495,11 @@
       </c>
       <c r="K48" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L48" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2250.2931596091207</v>
+        <v>2235.7281553398057</v>
       </c>
       <c r="M48" s="1">
         <v>46077</v>
@@ -12717,11 +12553,11 @@
       </c>
       <c r="K49" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L49" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2360.8338762214985</v>
+        <v>2345.5533980582522</v>
       </c>
       <c r="M49" s="1">
         <v>46080</v>
@@ -12775,11 +12611,11 @@
       </c>
       <c r="K50" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L50" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2256.8729641693812</v>
+        <v>2242.2653721682846</v>
       </c>
       <c r="M50" s="1">
         <v>46085</v>
@@ -12833,11 +12669,11 @@
       </c>
       <c r="K51" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L51" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2585.8631921824103</v>
+        <v>2569.1262135922325</v>
       </c>
       <c r="M51" s="1">
         <v>46087</v>
@@ -12891,11 +12727,11 @@
       </c>
       <c r="K52" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L52" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1839.7133550488602</v>
+        <v>1827.8058252427184</v>
       </c>
       <c r="M52" s="1">
         <v>46094</v>
@@ -12949,11 +12785,11 @@
       </c>
       <c r="K53" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L53" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2012.1042345276874</v>
+        <v>1999.0809061488669</v>
       </c>
       <c r="M53" s="1">
         <v>46095</v>
@@ -13007,11 +12843,11 @@
       </c>
       <c r="K54" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L54" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2080.5342019543978</v>
+        <v>2067.0679611650485</v>
       </c>
       <c r="M54" s="1">
         <v>46098</v>
@@ -13068,11 +12904,11 @@
       </c>
       <c r="K55" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L55" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1842.3452768729644</v>
+        <v>1830.42071197411</v>
       </c>
       <c r="M55" s="1">
         <v>46103</v>
@@ -13129,11 +12965,11 @@
       </c>
       <c r="K56" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L56" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2497.6938110749188</v>
+        <v>2481.5275080906149</v>
       </c>
       <c r="M56" s="1">
         <v>46106</v>
@@ -13190,11 +13026,11 @@
       </c>
       <c r="K57" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L57" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1984.4690553745929</v>
+        <v>1971.6245954692554</v>
       </c>
       <c r="M57" s="1">
         <v>46108</v>
@@ -13251,11 +13087,11 @@
       </c>
       <c r="K58" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L58" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2075.2703583061889</v>
+        <v>2061.8381877022653</v>
       </c>
       <c r="M58" s="1">
         <v>46107</v>
@@ -13312,11 +13148,11 @@
       </c>
       <c r="K59" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L59" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2331.8827361563517</v>
+        <v>2316.7896440129448</v>
       </c>
       <c r="M59" s="1">
         <v>46111</v>
@@ -13373,11 +13209,11 @@
       </c>
       <c r="K60" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L60" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2243.7133550488602</v>
+        <v>2229.1909385113267</v>
       </c>
       <c r="M60" s="1">
         <v>46112</v>
@@ -13434,11 +13270,11 @@
       </c>
       <c r="K61" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L61" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2392.4169381107495</v>
+        <v>2376.9320388349511</v>
       </c>
       <c r="M61" s="1">
         <v>46113</v>
@@ -13495,11 +13331,11 @@
       </c>
       <c r="K62" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L62" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1973.9413680781761</v>
+        <v>1961.1650485436892</v>
       </c>
       <c r="M62" s="1">
         <v>46118</v>
@@ -13556,11 +13392,11 @@
       </c>
       <c r="K63" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L63" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2431.8957654723131</v>
+        <v>2416.155339805825</v>
       </c>
       <c r="M63" s="1">
         <v>46120</v>
@@ -13617,11 +13453,11 @@
       </c>
       <c r="K64" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L64" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2133.1726384364824</v>
+        <v>2119.3656957928802</v>
       </c>
       <c r="M64" s="1">
         <v>46121</v>
@@ -13678,11 +13514,11 @@
       </c>
       <c r="K65" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L65" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2222.6579804560265</v>
+        <v>2208.2718446601939</v>
       </c>
       <c r="M65" s="1">
         <v>46125</v>
@@ -13739,11 +13575,11 @@
       </c>
       <c r="K66" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L66" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1987.1009771986971</v>
+        <v>1974.239482200647</v>
       </c>
       <c r="M66" s="1">
         <v>46127</v>
@@ -13800,11 +13636,11 @@
       </c>
       <c r="K67" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L67" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2126.5928338762214</v>
+        <v>2112.8284789644013</v>
       </c>
       <c r="M67" s="1">
         <v>46129</v>
@@ -13861,11 +13697,11 @@
       </c>
       <c r="K68" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L68" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2109.4853420195441</v>
+        <v>2095.8317152103559</v>
       </c>
       <c r="M68" s="1">
         <v>46143</v>
@@ -13922,11 +13758,11 @@
       </c>
       <c r="K69" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L69" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1968.6775244299677</v>
+        <v>1955.935275080906</v>
       </c>
       <c r="M69" s="1">
         <v>46147</v>
@@ -13983,11 +13819,11 @@
       </c>
       <c r="K70" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L70" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1851.5570032573291</v>
+        <v>1839.5728155339805</v>
       </c>
       <c r="M70" s="1">
         <v>46134</v>
@@ -14044,11 +13880,11 @@
       </c>
       <c r="K71" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L71" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1894.9837133550491</v>
+        <v>1882.7184466019417</v>
       </c>
       <c r="M71" s="1">
         <v>46136</v>
@@ -14105,11 +13941,11 @@
       </c>
       <c r="K72" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L72" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1931.8306188925083</v>
+        <v>1919.3268608414237</v>
       </c>
       <c r="M72" s="1">
         <v>46157</v>
@@ -14166,11 +14002,11 @@
       </c>
       <c r="K73" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L73" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1951.5700325732901</v>
+        <v>1938.9385113268606</v>
       </c>
       <c r="M73" s="1">
         <v>46161</v>
@@ -14227,11 +14063,11 @@
       </c>
       <c r="K74" s="2">
         <f t="shared" si="1"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L74" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2059.4788273615636</v>
+        <v>2046.1488673139156</v>
       </c>
       <c r="M74" s="1">
         <v>46164</v>
@@ -14288,11 +14124,11 @@
       </c>
       <c r="K75" s="2">
         <f t="shared" ref="K75:K106" si="2">IF(I75="$", J75/$H$1, IF(I75="U$D", J75*1, 0))</f>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L75" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1867.3485342019544</v>
+        <v>1855.2621359223299</v>
       </c>
       <c r="M75" s="1">
         <v>46150</v>
@@ -14343,11 +14179,11 @@
       </c>
       <c r="K76" s="2">
         <f t="shared" si="2"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L76" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2113.4332247557004</v>
+        <v>2099.754045307443</v>
       </c>
       <c r="M76" s="1">
         <v>46162</v>
@@ -14398,11 +14234,11 @@
       </c>
       <c r="K77" s="2">
         <f t="shared" si="2"/>
-        <v>65.798045602605868</v>
+        <v>65.372168284789637</v>
       </c>
       <c r="L77" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1950.254071661238</v>
+        <v>1937.6310679611649</v>
       </c>
       <c r="M77" s="1">
         <v>46185</v>
@@ -14453,11 +14289,11 @@
       </c>
       <c r="K78" s="2">
         <f t="shared" si="2"/>
-        <v>89.576547231270354</v>
+        <v>88.996763754045304</v>
       </c>
       <c r="L78" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2579.8045602605862</v>
+        <v>2563.1067961165049</v>
       </c>
       <c r="M78" s="1">
         <v>46069</v>
@@ -14511,11 +14347,11 @@
       </c>
       <c r="K79" s="2">
         <f t="shared" si="2"/>
-        <v>89.576547231270354</v>
+        <v>88.996763754045304</v>
       </c>
       <c r="L79" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2533.2247557003257</v>
+        <v>2516.8284789644013</v>
       </c>
       <c r="M79" s="1">
         <v>46081</v>
@@ -14569,11 +14405,11 @@
       </c>
       <c r="K80" s="2">
         <f t="shared" si="2"/>
-        <v>89.576547231270354</v>
+        <v>88.996763754045304</v>
       </c>
       <c r="L80" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2579.8045602605862</v>
+        <v>2563.1067961165049</v>
       </c>
       <c r="M80" s="1">
         <v>46088</v>
@@ -14627,11 +14463,11 @@
       </c>
       <c r="K81" s="2">
         <f t="shared" si="2"/>
-        <v>89.576547231270354</v>
+        <v>88.996763754045304</v>
       </c>
       <c r="L81" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2579.8045602605862</v>
+        <v>2563.1067961165049</v>
       </c>
       <c r="M81" s="1">
         <v>46101</v>
@@ -14688,11 +14524,11 @@
       </c>
       <c r="K82" s="2">
         <f t="shared" si="2"/>
-        <v>89.576547231270354</v>
+        <v>88.996763754045304</v>
       </c>
       <c r="L82" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2508.1433224755701</v>
+        <v>2491.9093851132684</v>
       </c>
       <c r="M82" s="1">
         <v>46114</v>
@@ -14746,11 +14582,11 @@
       </c>
       <c r="K83" s="2">
         <f t="shared" si="2"/>
-        <v>89.576547231270354</v>
+        <v>88.996763754045304</v>
       </c>
       <c r="L83" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2472.3127035830621</v>
+        <v>2456.3106796116504</v>
       </c>
       <c r="M83" s="1">
         <v>46129</v>
@@ -14807,11 +14643,11 @@
       </c>
       <c r="K84" s="2">
         <f t="shared" si="2"/>
-        <v>89.576547231270354</v>
+        <v>88.996763754045304</v>
       </c>
       <c r="L84" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1325.7328990228013</v>
+        <v>1317.1521035598705</v>
       </c>
       <c r="M84" s="1">
         <v>46153</v>
@@ -14862,11 +14698,11 @@
       </c>
       <c r="K85" s="2">
         <f t="shared" si="2"/>
-        <v>100.9771986970684</v>
+        <v>100.32362459546925</v>
       </c>
       <c r="L85" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1494.4625407166125</v>
+        <v>1484.789644012945</v>
       </c>
       <c r="M85" s="1">
         <v>46153</v>
@@ -16107,7 +15943,7 @@
         <v>3.15</v>
       </c>
       <c r="K107" s="2">
-        <f t="shared" ref="K107:K112" si="3">IF(I107="$", J107/$H$1, IF(I107="U$D", J107*1, 0))</f>
+        <f t="shared" ref="K107:K113" si="3">IF(I107="$", J107/$H$1, IF(I107="U$D", J107*1, 0))</f>
         <v>3.15</v>
       </c>
       <c r="L107" s="2">
@@ -16322,13 +16158,16 @@
         <v>18</v>
       </c>
       <c r="D111">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
       </c>
       <c r="F111" t="s">
         <v>44</v>
+      </c>
+      <c r="G111" t="s">
+        <v>90</v>
       </c>
       <c r="H111" t="s">
         <v>52</v>
@@ -16347,17 +16186,20 @@
       </c>
       <c r="L111" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2550</v>
+        <v>850</v>
       </c>
       <c r="M111" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="N111" t="str">
         <f>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</f>
         <v>septiembre</v>
       </c>
       <c r="O111" t="s">
-        <v>24</v>
+        <v>31</v>
+      </c>
+      <c r="P111" t="s">
+        <v>189</v>
       </c>
       <c r="Q111">
         <v>4</v>
@@ -16371,19 +16213,22 @@
         <v>17</v>
       </c>
       <c r="B112" s="1">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="C112" t="s">
         <v>18</v>
       </c>
       <c r="D112">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E112" t="s">
         <v>19</v>
       </c>
       <c r="F112" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="G112" t="s">
+        <v>90</v>
       </c>
       <c r="H112" t="s">
         <v>52</v>
@@ -16394,15 +16239,15 @@
       </c>
       <c r="J112" s="2">
         <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</f>
-        <v>2.1156999999999999</v>
-      </c>
-      <c r="K112" s="2">
-        <f t="shared" si="3"/>
-        <v>2.1156999999999999</v>
-      </c>
-      <c r="L112" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="K112" s="43">
+        <f>IF(I112="$", J112/$H$1, IF(I112="U$D", J112*1, 0))</f>
+        <v>0.85</v>
+      </c>
+      <c r="L112" s="43">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2115.6999999999998</v>
+        <v>1700</v>
       </c>
       <c r="M112" s="1">
         <v>46295</v>
@@ -16420,59 +16265,111 @@
         <v>17</v>
       </c>
       <c r="B113" s="1">
-        <v>46253</v>
+        <v>46044</v>
       </c>
       <c r="C113" t="s">
         <v>18</v>
       </c>
       <c r="D113">
-        <v>30.76</v>
+        <v>1000</v>
       </c>
       <c r="E113" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="F113" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="G113" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="H113" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="I113" s="3" t="str">
         <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[[Descripcion]:[Moneda]],3,FALSE)</f>
-        <v>$</v>
+        <v>U$D</v>
       </c>
       <c r="J113" s="2">
         <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</f>
-        <v>101000</v>
+        <v>2.1156999999999999</v>
       </c>
       <c r="K113" s="2">
-        <f>IF(I113="$", J113/$H$1, IF(I113="U$D", J113*1, 0))</f>
-        <v>65.798045602605868</v>
+        <f t="shared" si="3"/>
+        <v>2.1156999999999999</v>
       </c>
       <c r="L113" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2023.9478827361565</v>
+        <v>2115.6999999999998</v>
       </c>
       <c r="M113" s="1">
-        <v>46254</v>
+        <v>46295</v>
       </c>
       <c r="N113" t="str">
         <f>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="O113" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>17</v>
+      </c>
+      <c r="B114" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C114" t="s">
+        <v>18</v>
+      </c>
+      <c r="D114">
+        <v>30.76</v>
+      </c>
+      <c r="E114" t="s">
+        <v>124</v>
+      </c>
+      <c r="F114" t="s">
+        <v>182</v>
+      </c>
+      <c r="G114" t="s">
+        <v>40</v>
+      </c>
+      <c r="H114" t="s">
+        <v>83</v>
+      </c>
+      <c r="I114" s="3" t="str">
+        <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[[Descripcion]:[Moneda]],3,FALSE)</f>
+        <v>$</v>
+      </c>
+      <c r="J114" s="2">
+        <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</f>
+        <v>101000</v>
+      </c>
+      <c r="K114" s="2">
+        <f>IF(I114="$", J114/$H$1, IF(I114="U$D", J114*1, 0))</f>
+        <v>65.372168284789637</v>
+      </c>
+      <c r="L114" s="2">
+        <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
+        <v>2010.8478964401293</v>
+      </c>
+      <c r="M114" s="1">
+        <v>46254</v>
+      </c>
+      <c r="N114" t="str">
+        <f>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</f>
         <v>agosto</v>
       </c>
-      <c r="O113" t="s">
+      <c r="O114" t="s">
         <v>31</v>
       </c>
-      <c r="P113" t="s">
+      <c r="P114" t="s">
         <v>183</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A10:P113">
-    <cfRule type="expression" dxfId="34" priority="1">
+  <conditionalFormatting sqref="A10:P114">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$O10="cumplido"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17196,7 +17093,7 @@
       <c r="A4" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="41">
+      <c r="B4">
         <v>221817.46</v>
       </c>
     </row>
@@ -17204,7 +17101,7 @@
       <c r="A5" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="41">
+      <c r="B5">
         <v>31470</v>
       </c>
     </row>
@@ -17212,7 +17109,7 @@
       <c r="A6" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="41">
+      <c r="B6">
         <v>200</v>
       </c>
     </row>
@@ -17220,7 +17117,7 @@
       <c r="A7" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="41">
+      <c r="B7">
         <v>3000</v>
       </c>
     </row>
@@ -17228,7 +17125,7 @@
       <c r="A8" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="41">
+      <c r="B8">
         <v>46000</v>
       </c>
     </row>
@@ -17236,7 +17133,7 @@
       <c r="A9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="41">
+      <c r="B9">
         <v>6000</v>
       </c>
     </row>
@@ -17244,7 +17141,7 @@
       <c r="A10" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="41">
+      <c r="B10">
         <v>700</v>
       </c>
     </row>
@@ -17252,7 +17149,7 @@
       <c r="A11" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="41">
+      <c r="B11">
         <v>1000</v>
       </c>
     </row>
@@ -17260,7 +17157,7 @@
       <c r="A12" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12">
         <v>2400</v>
       </c>
     </row>
@@ -17268,7 +17165,7 @@
       <c r="A13" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13">
         <v>12250</v>
       </c>
     </row>
@@ -17276,7 +17173,7 @@
       <c r="A14" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="41">
+      <c r="B14">
         <v>1198.58</v>
       </c>
     </row>
@@ -17284,7 +17181,7 @@
       <c r="A15" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="41">
+      <c r="B15">
         <v>185.08</v>
       </c>
     </row>
@@ -17292,7 +17189,7 @@
       <c r="A16" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="41">
+      <c r="B16">
         <v>2100</v>
       </c>
     </row>
@@ -17300,7 +17197,7 @@
       <c r="A17" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="41">
+      <c r="B17">
         <v>3574</v>
       </c>
     </row>
@@ -17308,7 +17205,7 @@
       <c r="A18" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="41">
+      <c r="B18">
         <v>110200</v>
       </c>
     </row>
@@ -17316,7 +17213,7 @@
       <c r="A19" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="41">
+      <c r="B19">
         <v>1525</v>
       </c>
     </row>
@@ -17324,7 +17221,7 @@
       <c r="A20" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="B20" s="41">
+      <c r="B20">
         <v>14.8</v>
       </c>
     </row>
@@ -17332,7 +17229,7 @@
       <c r="A21" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="41">
+      <c r="B21">
         <v>4500</v>
       </c>
     </row>
@@ -17340,7 +17237,7 @@
       <c r="A22" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="41">
+      <c r="B22">
         <v>500</v>
       </c>
     </row>
@@ -17348,7 +17245,7 @@
       <c r="A23" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="41">
+      <c r="B23">
         <v>3000</v>
       </c>
     </row>
@@ -17356,7 +17253,7 @@
       <c r="A24" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="41">
+      <c r="B24">
         <v>1000</v>
       </c>
     </row>
@@ -17364,7 +17261,7 @@
       <c r="A25" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="41">
+      <c r="B25">
         <v>226317.46</v>
       </c>
     </row>
@@ -18211,7 +18108,6 @@
       <c r="A4" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="41"/>
       <c r="F4" s="7"/>
     </row>
   </sheetData>
@@ -18272,7 +18168,7 @@
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5">
         <v>3000</v>
       </c>
       <c r="E5" s="27">
@@ -18286,7 +18182,7 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6">
         <v>1000</v>
       </c>
       <c r="E6" s="27">
@@ -18297,7 +18193,7 @@
       <c r="A7" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="40">
         <v>4000</v>
       </c>
       <c r="E7" s="27">
@@ -18305,7 +18201,6 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="41"/>
       <c r="E8" s="27"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -18318,7 +18213,7 @@
       <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9">
         <v>500</v>
       </c>
       <c r="E9" s="27">
@@ -18329,7 +18224,7 @@
       <c r="A10" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="40">
         <v>500</v>
       </c>
       <c r="E10" s="27">
@@ -18337,14 +18232,13 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D11" s="41"/>
       <c r="E11" s="27"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="41">
         <v>4500</v>
       </c>
       <c r="E12" s="27">
@@ -18404,7 +18298,7 @@
       <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="44">
+      <c r="D4">
         <v>700</v>
       </c>
     </row>
@@ -18415,7 +18309,7 @@
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5">
         <v>1000</v>
       </c>
     </row>
@@ -18423,7 +18317,7 @@
       <c r="B6" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6">
         <v>2400</v>
       </c>
     </row>
@@ -18434,7 +18328,7 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7">
         <v>15250</v>
       </c>
     </row>
@@ -18445,7 +18339,7 @@
       <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="44">
+      <c r="D8">
         <v>2100</v>
       </c>
     </row>
@@ -18456,7 +18350,7 @@
       <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9">
         <v>4574</v>
       </c>
     </row>
@@ -18467,12 +18361,9 @@
       <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10">
         <v>1525</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D11" s="41"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -18484,7 +18375,7 @@
       <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="44">
+      <c r="D12">
         <v>31470</v>
       </c>
     </row>
@@ -18495,7 +18386,7 @@
       <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="44">
+      <c r="D13">
         <v>200</v>
       </c>
     </row>
@@ -18506,7 +18397,7 @@
       <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14">
         <v>3000</v>
       </c>
     </row>
@@ -18517,7 +18408,7 @@
       <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="44">
+      <c r="D15">
         <v>46500</v>
       </c>
     </row>
@@ -18528,7 +18419,7 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16">
         <v>6000</v>
       </c>
     </row>
@@ -18539,7 +18430,7 @@
       <c r="C17" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17">
         <v>1198.58</v>
       </c>
     </row>
@@ -18550,7 +18441,7 @@
       <c r="C18" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18">
         <v>185.08</v>
       </c>
     </row>
@@ -18561,7 +18452,7 @@
       <c r="C19" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="44">
+      <c r="D19">
         <v>110200</v>
       </c>
     </row>
@@ -18572,18 +18463,15 @@
       <c r="C20" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20">
         <v>14.8</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D21" s="41"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22">
         <v>226317.46</v>
       </c>
     </row>
@@ -18644,7 +18532,7 @@
       <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="41">
+      <c r="F4">
         <v>700</v>
       </c>
       <c r="G4" s="7">
@@ -18664,7 +18552,7 @@
       <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5">
         <v>1000</v>
       </c>
       <c r="G5" s="7">
@@ -18684,7 +18572,7 @@
       <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6">
         <v>2400</v>
       </c>
       <c r="G6" s="7">
@@ -18704,7 +18592,7 @@
       <c r="E7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7">
         <v>15250</v>
       </c>
       <c r="G7" s="7">
@@ -18724,7 +18612,7 @@
       <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8">
         <v>2100</v>
       </c>
       <c r="G8" s="7">
@@ -18744,7 +18632,7 @@
       <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9">
         <v>4574</v>
       </c>
       <c r="G9" s="7">
@@ -18764,7 +18652,7 @@
       <c r="E10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10">
         <v>1525</v>
       </c>
       <c r="G10" s="7">
@@ -18772,7 +18660,6 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F11" s="41"/>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -18791,7 +18678,7 @@
       <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12">
         <v>31470</v>
       </c>
       <c r="G12" s="7">
@@ -18811,7 +18698,7 @@
       <c r="E13" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13">
         <v>200</v>
       </c>
       <c r="G13" s="7">
@@ -18831,7 +18718,7 @@
       <c r="E14" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14">
         <v>3000</v>
       </c>
       <c r="G14" s="7">
@@ -18851,7 +18738,7 @@
       <c r="E15" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15">
         <v>46500</v>
       </c>
       <c r="G15" s="7">
@@ -18871,7 +18758,7 @@
       <c r="E16" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16">
         <v>6000</v>
       </c>
       <c r="G16" s="7">
@@ -18891,7 +18778,7 @@
       <c r="E17" t="s">
         <v>124</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17">
         <v>1198.58</v>
       </c>
       <c r="G17" s="7">
@@ -18911,7 +18798,7 @@
       <c r="E18" t="s">
         <v>124</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18">
         <v>185.08</v>
       </c>
       <c r="G18" s="7">
@@ -18931,7 +18818,7 @@
       <c r="E19" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19">
         <v>110200</v>
       </c>
       <c r="G19" s="7">
@@ -18951,7 +18838,7 @@
       <c r="E20" t="s">
         <v>124</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20">
         <v>14.8</v>
       </c>
       <c r="G20" s="7">
@@ -18959,14 +18846,13 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F21" s="41"/>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="45">
+      <c r="F22" s="42">
         <v>226317.46</v>
       </c>
       <c r="G22" s="7">
@@ -19044,7 +18930,7 @@
       <c r="E5" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5">
         <v>335</v>
       </c>
       <c r="G5" s="27">
@@ -19055,7 +18941,7 @@
       <c r="E6" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6">
         <v>335</v>
       </c>
       <c r="G6" s="27">
@@ -19066,7 +18952,7 @@
       <c r="E7" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7">
         <v>30</v>
       </c>
       <c r="G7" s="27">
@@ -19083,7 +18969,7 @@
       <c r="E8" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8">
         <v>1000</v>
       </c>
       <c r="G8" s="27">
@@ -19100,7 +18986,7 @@
       <c r="E9" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9">
         <v>500</v>
       </c>
       <c r="G9" s="27">
@@ -19111,7 +18997,7 @@
       <c r="E10" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10">
         <v>400</v>
       </c>
       <c r="G10" s="27">
@@ -19122,7 +19008,7 @@
       <c r="E11" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11">
         <v>1500</v>
       </c>
       <c r="G11" s="27">
@@ -19139,7 +19025,7 @@
       <c r="E12" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12">
         <v>4250</v>
       </c>
       <c r="G12" s="27">
@@ -19150,7 +19036,7 @@
       <c r="E13" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13">
         <v>2500</v>
       </c>
       <c r="G13" s="27">
@@ -19161,7 +19047,7 @@
       <c r="E14" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14">
         <v>500</v>
       </c>
       <c r="G14" s="27">
@@ -19172,7 +19058,7 @@
       <c r="E15" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15">
         <v>1000</v>
       </c>
       <c r="G15" s="27">
@@ -19183,7 +19069,7 @@
       <c r="E16" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16">
         <v>4000</v>
       </c>
       <c r="G16" s="27">
@@ -19200,7 +19086,7 @@
       <c r="E17" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17">
         <v>2000</v>
       </c>
       <c r="G17" s="27">
@@ -19211,7 +19097,7 @@
       <c r="E18" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18">
         <v>100</v>
       </c>
       <c r="G18" s="27">
@@ -19228,7 +19114,7 @@
       <c r="E19" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19">
         <v>774</v>
       </c>
       <c r="G19" s="27">
@@ -19239,7 +19125,7 @@
       <c r="E20" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20">
         <v>800</v>
       </c>
       <c r="G20" s="27">
@@ -19250,7 +19136,7 @@
       <c r="E21" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="41">
+      <c r="F21">
         <v>1000</v>
       </c>
       <c r="G21" s="27">
@@ -19261,7 +19147,7 @@
       <c r="E22" t="s">
         <v>45</v>
       </c>
-      <c r="F22" s="41">
+      <c r="F22">
         <v>1000</v>
       </c>
       <c r="G22" s="27">
@@ -19278,7 +19164,7 @@
       <c r="E23" t="s">
         <v>25</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23">
         <v>475</v>
       </c>
       <c r="G23" s="27">
@@ -19289,7 +19175,7 @@
       <c r="E24" t="s">
         <v>34</v>
       </c>
-      <c r="F24" s="41">
+      <c r="F24">
         <v>400</v>
       </c>
       <c r="G24" s="27">
@@ -19300,7 +19186,7 @@
       <c r="E25" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="41">
+      <c r="F25">
         <v>650</v>
       </c>
       <c r="G25" s="27">
@@ -19311,7 +19197,7 @@
       <c r="B26" t="s">
         <v>97</v>
       </c>
-      <c r="F26" s="41">
+      <c r="F26">
         <v>23549</v>
       </c>
       <c r="G26" s="27">
@@ -19331,7 +19217,7 @@
       <c r="E27" t="s">
         <v>188</v>
       </c>
-      <c r="F27" s="41">
+      <c r="F27">
         <v>3000</v>
       </c>
       <c r="G27" s="27">
@@ -19348,7 +19234,7 @@
       <c r="E28" t="s">
         <v>188</v>
       </c>
-      <c r="F28" s="41">
+      <c r="F28">
         <v>1000</v>
       </c>
       <c r="G28" s="27">
@@ -19359,7 +19245,7 @@
       <c r="B29" t="s">
         <v>98</v>
       </c>
-      <c r="F29" s="41">
+      <c r="F29">
         <v>4000</v>
       </c>
       <c r="G29" s="27">
@@ -19370,7 +19256,7 @@
       <c r="A30" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="42">
+      <c r="F30" s="40">
         <v>27549</v>
       </c>
       <c r="G30" s="27">
@@ -19378,7 +19264,6 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F31" s="41"/>
       <c r="G31" s="27"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -19397,7 +19282,7 @@
       <c r="E32" t="s">
         <v>23</v>
       </c>
-      <c r="F32" s="41">
+      <c r="F32">
         <v>8670</v>
       </c>
       <c r="G32" s="27">
@@ -19408,7 +19293,7 @@
       <c r="E33" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="41">
+      <c r="F33">
         <v>12000</v>
       </c>
       <c r="G33" s="27">
@@ -19419,7 +19304,7 @@
       <c r="E34" t="s">
         <v>34</v>
       </c>
-      <c r="F34" s="41">
+      <c r="F34">
         <v>4800</v>
       </c>
       <c r="G34" s="27">
@@ -19430,7 +19315,7 @@
       <c r="E35" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="41">
+      <c r="F35">
         <v>6000</v>
       </c>
       <c r="G35" s="27">
@@ -19447,7 +19332,7 @@
       <c r="E36" t="s">
         <v>25</v>
       </c>
-      <c r="F36" s="41">
+      <c r="F36">
         <v>200</v>
       </c>
       <c r="G36" s="27">
@@ -19464,7 +19349,7 @@
       <c r="E37" t="s">
         <v>25</v>
       </c>
-      <c r="F37" s="41">
+      <c r="F37">
         <v>3000</v>
       </c>
       <c r="G37" s="27">
@@ -19481,7 +19366,7 @@
       <c r="E38" t="s">
         <v>30</v>
       </c>
-      <c r="F38" s="41">
+      <c r="F38">
         <v>7000</v>
       </c>
       <c r="G38" s="27">
@@ -19492,7 +19377,7 @@
       <c r="E39" t="s">
         <v>23</v>
       </c>
-      <c r="F39" s="41">
+      <c r="F39">
         <v>10000</v>
       </c>
       <c r="G39" s="27">
@@ -19503,7 +19388,7 @@
       <c r="E40" t="s">
         <v>25</v>
       </c>
-      <c r="F40" s="41">
+      <c r="F40">
         <v>14000</v>
       </c>
       <c r="G40" s="27">
@@ -19514,7 +19399,7 @@
       <c r="E41" t="s">
         <v>34</v>
       </c>
-      <c r="F41" s="41">
+      <c r="F41">
         <v>12000</v>
       </c>
       <c r="G41" s="27">
@@ -19525,7 +19410,7 @@
       <c r="E42" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="41">
+      <c r="F42">
         <v>3000</v>
       </c>
       <c r="G42" s="27">
@@ -19542,7 +19427,7 @@
       <c r="E43" t="s">
         <v>23</v>
       </c>
-      <c r="F43" s="41">
+      <c r="F43">
         <v>5000</v>
       </c>
       <c r="G43" s="27">
@@ -19553,7 +19438,7 @@
       <c r="E44" t="s">
         <v>25</v>
       </c>
-      <c r="F44" s="41">
+      <c r="F44">
         <v>1000</v>
       </c>
       <c r="G44" s="27">
@@ -19570,7 +19455,7 @@
       <c r="E45" t="s">
         <v>30</v>
       </c>
-      <c r="F45" s="41">
+      <c r="F45">
         <v>72.06</v>
       </c>
       <c r="G45" s="27">
@@ -19581,7 +19466,7 @@
       <c r="E46" t="s">
         <v>23</v>
       </c>
-      <c r="F46" s="41">
+      <c r="F46">
         <v>203.38</v>
       </c>
       <c r="G46" s="27">
@@ -19592,7 +19477,7 @@
       <c r="E47" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="41">
+      <c r="F47">
         <v>360.96000000000004</v>
       </c>
       <c r="G47" s="27">
@@ -19603,7 +19488,7 @@
       <c r="E48" t="s">
         <v>34</v>
       </c>
-      <c r="F48" s="41">
+      <c r="F48">
         <v>288.98</v>
       </c>
       <c r="G48" s="27">
@@ -19614,7 +19499,7 @@
       <c r="E49" t="s">
         <v>42</v>
       </c>
-      <c r="F49" s="41">
+      <c r="F49">
         <v>212.8</v>
       </c>
       <c r="G49" s="27">
@@ -19625,7 +19510,7 @@
       <c r="E50" t="s">
         <v>45</v>
       </c>
-      <c r="F50" s="41">
+      <c r="F50">
         <v>29.64</v>
       </c>
       <c r="G50" s="27">
@@ -19636,7 +19521,7 @@
       <c r="E51" t="s">
         <v>185</v>
       </c>
-      <c r="F51" s="41">
+      <c r="F51">
         <v>30.76</v>
       </c>
       <c r="G51" s="27">
@@ -19653,7 +19538,7 @@
       <c r="E52" t="s">
         <v>23</v>
       </c>
-      <c r="F52" s="41">
+      <c r="F52">
         <v>57.08</v>
       </c>
       <c r="G52" s="27">
@@ -19664,7 +19549,7 @@
       <c r="E53" t="s">
         <v>25</v>
       </c>
-      <c r="F53" s="41">
+      <c r="F53">
         <v>57.6</v>
       </c>
       <c r="G53" s="27">
@@ -19675,7 +19560,7 @@
       <c r="E54" t="s">
         <v>34</v>
       </c>
-      <c r="F54" s="41">
+      <c r="F54">
         <v>55.6</v>
       </c>
       <c r="G54" s="27">
@@ -19686,7 +19571,7 @@
       <c r="E55" t="s">
         <v>42</v>
       </c>
-      <c r="F55" s="41">
+      <c r="F55">
         <v>14.8</v>
       </c>
       <c r="G55" s="27">
@@ -19703,7 +19588,7 @@
       <c r="E56" t="s">
         <v>30</v>
       </c>
-      <c r="F56" s="41">
+      <c r="F56">
         <v>37000</v>
       </c>
       <c r="G56" s="27">
@@ -19714,7 +19599,7 @@
       <c r="E57" t="s">
         <v>25</v>
       </c>
-      <c r="F57" s="41">
+      <c r="F57">
         <v>28800</v>
       </c>
       <c r="G57" s="27">
@@ -19725,7 +19610,7 @@
       <c r="E58" t="s">
         <v>34</v>
       </c>
-      <c r="F58" s="41">
+      <c r="F58">
         <v>42000</v>
       </c>
       <c r="G58" s="27">
@@ -19736,7 +19621,7 @@
       <c r="E59" t="s">
         <v>42</v>
       </c>
-      <c r="F59" s="41">
+      <c r="F59">
         <v>2400</v>
       </c>
       <c r="G59" s="27">
@@ -19753,7 +19638,7 @@
       <c r="E60" t="s">
         <v>42</v>
       </c>
-      <c r="F60" s="41">
+      <c r="F60">
         <v>14.8</v>
       </c>
       <c r="G60" s="27">
@@ -19764,7 +19649,7 @@
       <c r="B61" t="s">
         <v>97</v>
       </c>
-      <c r="F61" s="41">
+      <c r="F61">
         <v>198268.46000000002</v>
       </c>
       <c r="G61" s="27">
@@ -19784,7 +19669,7 @@
       <c r="E62" t="s">
         <v>188</v>
       </c>
-      <c r="F62" s="41">
+      <c r="F62">
         <v>500</v>
       </c>
       <c r="G62" s="27">
@@ -19795,7 +19680,7 @@
       <c r="B63" t="s">
         <v>98</v>
       </c>
-      <c r="F63" s="41">
+      <c r="F63">
         <v>500</v>
       </c>
       <c r="G63" s="27">
@@ -19806,7 +19691,7 @@
       <c r="A64" t="s">
         <v>84</v>
       </c>
-      <c r="F64" s="42">
+      <c r="F64" s="40">
         <v>198768.46000000002</v>
       </c>
       <c r="G64" s="27">
@@ -19814,14 +19699,13 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F65" s="41"/>
       <c r="G65" s="27"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>53</v>
       </c>
-      <c r="F66" s="43">
+      <c r="F66" s="41">
         <v>226317.46000000002</v>
       </c>
       <c r="G66" s="27">
@@ -19884,7 +19768,7 @@
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5">
         <v>7000</v>
       </c>
       <c r="E5" s="27">
@@ -19898,7 +19782,7 @@
       <c r="C6" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6">
         <v>72.06</v>
       </c>
       <c r="E6" s="27">
@@ -19912,7 +19796,7 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7">
         <v>37000</v>
       </c>
       <c r="E7" s="27">
@@ -19923,7 +19807,7 @@
       <c r="A8" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8">
         <v>44072.06</v>
       </c>
       <c r="E8" s="27">
@@ -19940,7 +19824,7 @@
       <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9">
         <v>8670</v>
       </c>
       <c r="E9" s="27">
@@ -19954,7 +19838,7 @@
       <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10">
         <v>10000</v>
       </c>
       <c r="E10" s="27">
@@ -19968,7 +19852,7 @@
       <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11">
         <v>5000</v>
       </c>
       <c r="E11" s="27">
@@ -19982,7 +19866,7 @@
       <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12">
         <v>4250</v>
       </c>
       <c r="E12" s="27">
@@ -19996,7 +19880,7 @@
       <c r="C13" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13">
         <v>203.38</v>
       </c>
       <c r="E13" s="27">
@@ -20010,7 +19894,7 @@
       <c r="C14" t="s">
         <v>124</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14">
         <v>57.08</v>
       </c>
       <c r="E14" s="27">
@@ -20024,7 +19908,7 @@
       <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15">
         <v>2000</v>
       </c>
       <c r="E15" s="27">
@@ -20038,7 +19922,7 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16">
         <v>774</v>
       </c>
       <c r="E16" s="27">
@@ -20049,7 +19933,7 @@
       <c r="A17" t="s">
         <v>129</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17">
         <v>30954.460000000003</v>
       </c>
       <c r="E17" s="27">
@@ -20066,7 +19950,7 @@
       <c r="C18" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18">
         <v>12000</v>
       </c>
       <c r="E18" s="27">
@@ -20080,7 +19964,7 @@
       <c r="C19" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19">
         <v>200</v>
       </c>
       <c r="E19" s="27">
@@ -20094,7 +19978,7 @@
       <c r="C20" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20">
         <v>3000</v>
       </c>
       <c r="E20" s="27">
@@ -20108,7 +19992,7 @@
       <c r="C21" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21">
         <v>14000</v>
       </c>
       <c r="E21" s="27">
@@ -20122,7 +20006,7 @@
       <c r="C22" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22">
         <v>1000</v>
       </c>
       <c r="E22" s="27">
@@ -20136,7 +20020,7 @@
       <c r="C23" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23">
         <v>500</v>
       </c>
       <c r="E23" s="27">
@@ -20150,7 +20034,7 @@
       <c r="C24" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24">
         <v>2500</v>
       </c>
       <c r="E24" s="27">
@@ -20164,7 +20048,7 @@
       <c r="C25" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25">
         <v>360.96000000000004</v>
       </c>
       <c r="E25" s="27">
@@ -20178,7 +20062,7 @@
       <c r="C26" t="s">
         <v>124</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26">
         <v>57.6</v>
       </c>
       <c r="E26" s="27">
@@ -20192,7 +20076,7 @@
       <c r="C27" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="41">
+      <c r="D27">
         <v>800</v>
       </c>
       <c r="E27" s="27">
@@ -20206,7 +20090,7 @@
       <c r="C28" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="41">
+      <c r="D28">
         <v>28800</v>
       </c>
       <c r="E28" s="27">
@@ -20220,7 +20104,7 @@
       <c r="C29" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="41">
+      <c r="D29">
         <v>475</v>
       </c>
       <c r="E29" s="27">
@@ -20231,7 +20115,7 @@
       <c r="A30" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30">
         <v>63693.56</v>
       </c>
       <c r="E30" s="27">
@@ -20248,7 +20132,7 @@
       <c r="C31" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="41">
+      <c r="D31">
         <v>4800</v>
       </c>
       <c r="E31" s="27">
@@ -20262,7 +20146,7 @@
       <c r="C32" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="41">
+      <c r="D32">
         <v>12000</v>
       </c>
       <c r="E32" s="27">
@@ -20276,7 +20160,7 @@
       <c r="C33" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="41">
+      <c r="D33">
         <v>400</v>
       </c>
       <c r="E33" s="27">
@@ -20290,7 +20174,7 @@
       <c r="C34" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="41">
+      <c r="D34">
         <v>500</v>
       </c>
       <c r="E34" s="27">
@@ -20304,7 +20188,7 @@
       <c r="C35" t="s">
         <v>124</v>
       </c>
-      <c r="D35" s="41">
+      <c r="D35">
         <v>288.98</v>
       </c>
       <c r="E35" s="27">
@@ -20318,7 +20202,7 @@
       <c r="C36" t="s">
         <v>124</v>
       </c>
-      <c r="D36" s="41">
+      <c r="D36">
         <v>55.6</v>
       </c>
       <c r="E36" s="27">
@@ -20332,7 +20216,7 @@
       <c r="C37" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="41">
+      <c r="D37">
         <v>42000</v>
       </c>
       <c r="E37" s="27">
@@ -20346,7 +20230,7 @@
       <c r="C38" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="41">
+      <c r="D38">
         <v>400</v>
       </c>
       <c r="E38" s="27">
@@ -20357,7 +20241,7 @@
       <c r="A39" t="s">
         <v>101</v>
       </c>
-      <c r="D39" s="41">
+      <c r="D39">
         <v>60444.58</v>
       </c>
       <c r="E39" s="27">
@@ -20374,7 +20258,7 @@
       <c r="C40" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="41">
+      <c r="D40">
         <v>6000</v>
       </c>
       <c r="E40" s="27">
@@ -20388,7 +20272,7 @@
       <c r="C41" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="41">
+      <c r="D41">
         <v>3000</v>
       </c>
       <c r="E41" s="27">
@@ -20402,7 +20286,7 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="41">
+      <c r="D42">
         <v>335</v>
       </c>
       <c r="E42" s="27">
@@ -20416,7 +20300,7 @@
       <c r="C43" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="41">
+      <c r="D43">
         <v>1500</v>
       </c>
       <c r="E43" s="27">
@@ -20430,7 +20314,7 @@
       <c r="C44" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="41">
+      <c r="D44">
         <v>1000</v>
       </c>
       <c r="E44" s="27">
@@ -20444,7 +20328,7 @@
       <c r="C45" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="41">
+      <c r="D45">
         <v>212.8</v>
       </c>
       <c r="E45" s="27">
@@ -20458,7 +20342,7 @@
       <c r="C46" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="41">
+      <c r="D46">
         <v>14.8</v>
       </c>
       <c r="E46" s="27">
@@ -20472,7 +20356,7 @@
       <c r="C47" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="41">
+      <c r="D47">
         <v>100</v>
       </c>
       <c r="E47" s="27">
@@ -20489,7 +20373,7 @@
       <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="41">
+      <c r="D48">
         <v>1000</v>
       </c>
       <c r="E48" s="27">
@@ -20503,7 +20387,7 @@
       <c r="C49" t="s">
         <v>19</v>
       </c>
-      <c r="D49" s="41">
+      <c r="D49">
         <v>2400</v>
       </c>
       <c r="E49" s="27">
@@ -20517,7 +20401,7 @@
       <c r="C50" t="s">
         <v>19</v>
       </c>
-      <c r="D50" s="41">
+      <c r="D50">
         <v>650</v>
       </c>
       <c r="E50" s="27">
@@ -20531,7 +20415,7 @@
       <c r="C51" t="s">
         <v>124</v>
       </c>
-      <c r="D51" s="41">
+      <c r="D51">
         <v>14.8</v>
       </c>
       <c r="E51" s="27">
@@ -20542,7 +20426,7 @@
       <c r="A52" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="41">
+      <c r="D52">
         <v>16227.399999999998</v>
       </c>
       <c r="E52" s="27">
@@ -20559,7 +20443,7 @@
       <c r="C53" t="s">
         <v>19</v>
       </c>
-      <c r="D53" s="41">
+      <c r="D53">
         <v>335</v>
       </c>
       <c r="E53" s="27">
@@ -20573,7 +20457,7 @@
       <c r="C54" t="s">
         <v>19</v>
       </c>
-      <c r="D54" s="41">
+      <c r="D54">
         <v>1000</v>
       </c>
       <c r="E54" s="27">
@@ -20587,7 +20471,7 @@
       <c r="C55" t="s">
         <v>19</v>
       </c>
-      <c r="D55" s="41">
+      <c r="D55">
         <v>4000</v>
       </c>
       <c r="E55" s="27">
@@ -20601,7 +20485,7 @@
       <c r="C56" t="s">
         <v>124</v>
       </c>
-      <c r="D56" s="41">
+      <c r="D56">
         <v>29.64</v>
       </c>
       <c r="E56" s="27">
@@ -20615,7 +20499,7 @@
       <c r="C57" t="s">
         <v>19</v>
       </c>
-      <c r="D57" s="41">
+      <c r="D57">
         <v>1000</v>
       </c>
       <c r="E57" s="27">
@@ -20626,7 +20510,7 @@
       <c r="A58" t="s">
         <v>176</v>
       </c>
-      <c r="D58" s="41">
+      <c r="D58">
         <v>6364.64</v>
       </c>
       <c r="E58" s="27">
@@ -20643,7 +20527,7 @@
       <c r="C59" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="41">
+      <c r="D59">
         <v>30</v>
       </c>
       <c r="E59" s="27">
@@ -20654,7 +20538,7 @@
       <c r="A60" t="s">
         <v>186</v>
       </c>
-      <c r="D60" s="41">
+      <c r="D60">
         <v>30</v>
       </c>
       <c r="E60" s="27">
@@ -20671,7 +20555,7 @@
       <c r="C61" t="s">
         <v>124</v>
       </c>
-      <c r="D61" s="41">
+      <c r="D61">
         <v>30.76</v>
       </c>
       <c r="E61" s="27">
@@ -20682,7 +20566,7 @@
       <c r="A62" t="s">
         <v>187</v>
       </c>
-      <c r="D62" s="41">
+      <c r="D62">
         <v>30.76</v>
       </c>
       <c r="E62" s="27">
@@ -20693,7 +20577,7 @@
       <c r="A63" t="s">
         <v>53</v>
       </c>
-      <c r="D63" s="43">
+      <c r="D63" s="41">
         <v>221817.46000000002</v>
       </c>
       <c r="E63" s="27">

--- a/public/data/pedido quimicos campaña 2026 valorizado.xlsx
+++ b/public/data/pedido quimicos campaña 2026 valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fincalaseis-my.sharepoint.com/personal/compras_fincalaseis_com_ar/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2191" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{582D91A9-F974-4631-A89E-9810F01314D0}"/>
+  <xr:revisionPtr revIDLastSave="2197" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE95267E-728D-4B74-83FB-668C9B036283}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8EF26D9B-9BDD-40EA-9926-EAD75B18C35F}"/>
   </bookViews>
@@ -32,7 +32,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId13"/>
+    <pivotCache cacheId="10" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="190">
   <si>
     <t>Solicita</t>
   </si>
@@ -868,7 +868,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -948,7 +948,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1273,22 +1272,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>561951</xdr:colOff>
+      <xdr:colOff>603564</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>9430</xdr:rowOff>
+      <xdr:rowOff>9431</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1087951</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>9431</xdr:rowOff>
+      <xdr:colOff>1027946</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>180310</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B82B9736-1973-2A46-643C-798242246E85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C56C334A-95D1-454B-B9BA-618C402BB364}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1304,8 +1303,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6541010" y="198044"/>
-          <a:ext cx="2129218" cy="1178837"/>
+          <a:off x="6582623" y="198045"/>
+          <a:ext cx="2027600" cy="1161102"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4522,7 +4521,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:F4" firstHeaderRow="0" firstDataRow="1" firstDataCol="4"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5164,7 +5163,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:E12" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5851,7 +5850,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:D22" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -6538,7 +6537,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:G22" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -7271,7 +7270,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:G66" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -8174,7 +8173,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:E63" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -9048,7 +9047,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -10150,7 +10149,7 @@
         <v>159</v>
       </c>
       <c r="H1" s="8">
-        <v>1545</v>
+        <v>1550</v>
       </c>
       <c r="I1" s="2"/>
     </row>
@@ -10175,11 +10174,11 @@
       </c>
       <c r="K3" s="27">
         <f>SUM(L3:M3)</f>
-        <v>314882.08414239483</v>
+        <v>314571.40645161289</v>
       </c>
       <c r="L3" s="28">
         <f>SUMIFS(L:L, H:H, "INSUMOS DE CAMPAÑA", O:O, "Cumplido")</f>
-        <v>314882.08414239483</v>
+        <v>314571.40645161289</v>
       </c>
       <c r="M3" s="29">
         <f>SUMIFS(L:L, H:H, "INSUMOS DE CAMPAÑA", O:O, "Pendiente")</f>
@@ -10214,11 +10213,11 @@
       </c>
       <c r="K6" s="34">
         <f>SUM(K3:K5)</f>
-        <v>372204.29594239482</v>
+        <v>371893.61825161288</v>
       </c>
       <c r="L6" s="34">
         <f>SUM(L3:L5)</f>
-        <v>368388.59594239481</v>
+        <v>368077.91825161286</v>
       </c>
       <c r="M6" s="35">
         <f>SUM(M3:M5)</f>
@@ -10231,15 +10230,15 @@
       </c>
       <c r="K7" s="36">
         <f>K6*H1</f>
-        <v>575055637.23099995</v>
+        <v>576435108.28999996</v>
       </c>
       <c r="L7" s="36">
         <f>L6*H1</f>
-        <v>569160380.73099995</v>
+        <v>570520773.28999996</v>
       </c>
       <c r="M7" s="37">
         <f>M6*H1</f>
-        <v>5895256.5</v>
+        <v>5914335</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -10583,6 +10582,9 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
       <c r="B15" s="1">
         <v>46041</v>
       </c>
@@ -12147,11 +12149,11 @@
       </c>
       <c r="K42" s="2">
         <f t="shared" si="0"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L42" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2355.3592233009708</v>
+        <v>2347.7612903225804</v>
       </c>
       <c r="M42" s="1">
         <v>46037</v>
@@ -12205,11 +12207,11 @@
       </c>
       <c r="K43" s="2">
         <f t="shared" ref="K43:K74" si="1">IF(I43="$", J43/$H$1, IF(I43="U$D", J43*1, 0))</f>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L43" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2355.3592233009708</v>
+        <v>2347.7612903225804</v>
       </c>
       <c r="M43" s="1">
         <v>46037</v>
@@ -12263,11 +12265,11 @@
       </c>
       <c r="K44" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L44" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2404.3883495145628</v>
+        <v>2396.632258064516</v>
       </c>
       <c r="M44" s="1">
         <v>46063</v>
@@ -12321,11 +12323,11 @@
       </c>
       <c r="K45" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L45" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2404.3883495145628</v>
+        <v>2396.632258064516</v>
       </c>
       <c r="M45" s="1">
         <v>46066</v>
@@ -12379,11 +12381,11 @@
       </c>
       <c r="K46" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L46" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1734.9773462783169</v>
+        <v>1729.3806451612902</v>
       </c>
       <c r="M46" s="1">
         <v>46070</v>
@@ -12437,11 +12439,11 @@
       </c>
       <c r="K47" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L47" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2170.3559870550162</v>
+        <v>2163.3548387096776</v>
       </c>
       <c r="M47" s="1">
         <v>46073</v>
@@ -12495,11 +12497,11 @@
       </c>
       <c r="K48" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L48" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2235.7281553398057</v>
+        <v>2228.516129032258</v>
       </c>
       <c r="M48" s="1">
         <v>46077</v>
@@ -12553,11 +12555,11 @@
       </c>
       <c r="K49" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L49" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2345.5533980582522</v>
+        <v>2337.9870967741936</v>
       </c>
       <c r="M49" s="1">
         <v>46080</v>
@@ -12611,11 +12613,11 @@
       </c>
       <c r="K50" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L50" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2242.2653721682846</v>
+        <v>2235.0322580645156</v>
       </c>
       <c r="M50" s="1">
         <v>46085</v>
@@ -12669,11 +12671,11 @@
       </c>
       <c r="K51" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L51" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2569.1262135922325</v>
+        <v>2560.838709677419</v>
       </c>
       <c r="M51" s="1">
         <v>46087</v>
@@ -12727,11 +12729,11 @@
       </c>
       <c r="K52" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L52" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1827.8058252427184</v>
+        <v>1821.9096774193547</v>
       </c>
       <c r="M52" s="1">
         <v>46094</v>
@@ -12785,11 +12787,11 @@
       </c>
       <c r="K53" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L53" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1999.0809061488669</v>
+        <v>1992.6322580645158</v>
       </c>
       <c r="M53" s="1">
         <v>46095</v>
@@ -12843,11 +12845,11 @@
       </c>
       <c r="K54" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L54" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2067.0679611650485</v>
+        <v>2060.4</v>
       </c>
       <c r="M54" s="1">
         <v>46098</v>
@@ -12904,11 +12906,11 @@
       </c>
       <c r="K55" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L55" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1830.42071197411</v>
+        <v>1824.516129032258</v>
       </c>
       <c r="M55" s="1">
         <v>46103</v>
@@ -12965,11 +12967,11 @@
       </c>
       <c r="K56" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L56" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2481.5275080906149</v>
+        <v>2473.5225806451613</v>
       </c>
       <c r="M56" s="1">
         <v>46106</v>
@@ -13026,11 +13028,11 @@
       </c>
       <c r="K57" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L57" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1971.6245954692554</v>
+        <v>1965.264516129032</v>
       </c>
       <c r="M57" s="1">
         <v>46108</v>
@@ -13087,11 +13089,11 @@
       </c>
       <c r="K58" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L58" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2061.8381877022653</v>
+        <v>2055.1870967741934</v>
       </c>
       <c r="M58" s="1">
         <v>46107</v>
@@ -13148,11 +13150,11 @@
       </c>
       <c r="K59" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L59" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2316.7896440129448</v>
+        <v>2309.3161290322578</v>
       </c>
       <c r="M59" s="1">
         <v>46111</v>
@@ -13209,11 +13211,11 @@
       </c>
       <c r="K60" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L60" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2229.1909385113267</v>
+        <v>2222</v>
       </c>
       <c r="M60" s="1">
         <v>46112</v>
@@ -13270,11 +13272,11 @@
       </c>
       <c r="K61" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L61" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2376.9320388349511</v>
+        <v>2369.264516129032</v>
       </c>
       <c r="M61" s="1">
         <v>46113</v>
@@ -13331,11 +13333,11 @@
       </c>
       <c r="K62" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L62" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1961.1650485436892</v>
+        <v>1954.8387096774193</v>
       </c>
       <c r="M62" s="1">
         <v>46118</v>
@@ -13392,11 +13394,11 @@
       </c>
       <c r="K63" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L63" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2416.155339805825</v>
+        <v>2408.3612903225803</v>
       </c>
       <c r="M63" s="1">
         <v>46120</v>
@@ -13453,11 +13455,11 @@
       </c>
       <c r="K64" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L64" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2119.3656957928802</v>
+        <v>2112.5290322580645</v>
       </c>
       <c r="M64" s="1">
         <v>46121</v>
@@ -13514,11 +13516,11 @@
       </c>
       <c r="K65" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L65" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2208.2718446601939</v>
+        <v>2201.1483870967741</v>
       </c>
       <c r="M65" s="1">
         <v>46125</v>
@@ -13575,11 +13577,11 @@
       </c>
       <c r="K66" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L66" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1974.239482200647</v>
+        <v>1967.8709677419354</v>
       </c>
       <c r="M66" s="1">
         <v>46127</v>
@@ -13636,11 +13638,11 @@
       </c>
       <c r="K67" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L67" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2112.8284789644013</v>
+        <v>2106.0129032258064</v>
       </c>
       <c r="M67" s="1">
         <v>46129</v>
@@ -13697,11 +13699,11 @@
       </c>
       <c r="K68" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L68" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2095.8317152103559</v>
+        <v>2089.0709677419354</v>
       </c>
       <c r="M68" s="1">
         <v>46143</v>
@@ -13758,11 +13760,11 @@
       </c>
       <c r="K69" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L69" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1955.935275080906</v>
+        <v>1949.6258064516128</v>
       </c>
       <c r="M69" s="1">
         <v>46147</v>
@@ -13819,11 +13821,11 @@
       </c>
       <c r="K70" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L70" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1839.5728155339805</v>
+        <v>1833.6387096774192</v>
       </c>
       <c r="M70" s="1">
         <v>46134</v>
@@ -13880,11 +13882,11 @@
       </c>
       <c r="K71" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L71" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1882.7184466019417</v>
+        <v>1876.6451612903224</v>
       </c>
       <c r="M71" s="1">
         <v>46136</v>
@@ -13941,11 +13943,11 @@
       </c>
       <c r="K72" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L72" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1919.3268608414237</v>
+        <v>1913.1354838709676</v>
       </c>
       <c r="M72" s="1">
         <v>46157</v>
@@ -14002,11 +14004,11 @@
       </c>
       <c r="K73" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L73" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1938.9385113268606</v>
+        <v>1932.6838709677418</v>
       </c>
       <c r="M73" s="1">
         <v>46161</v>
@@ -14063,11 +14065,11 @@
       </c>
       <c r="K74" s="2">
         <f t="shared" si="1"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L74" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2046.1488673139156</v>
+        <v>2039.5483870967741</v>
       </c>
       <c r="M74" s="1">
         <v>46164</v>
@@ -14124,11 +14126,11 @@
       </c>
       <c r="K75" s="2">
         <f t="shared" ref="K75:K106" si="2">IF(I75="$", J75/$H$1, IF(I75="U$D", J75*1, 0))</f>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L75" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1855.2621359223299</v>
+        <v>1849.2774193548385</v>
       </c>
       <c r="M75" s="1">
         <v>46150</v>
@@ -14179,11 +14181,11 @@
       </c>
       <c r="K76" s="2">
         <f t="shared" si="2"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L76" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2099.754045307443</v>
+        <v>2092.9806451612899</v>
       </c>
       <c r="M76" s="1">
         <v>46162</v>
@@ -14234,11 +14236,11 @@
       </c>
       <c r="K77" s="2">
         <f t="shared" si="2"/>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L77" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1937.6310679611649</v>
+        <v>1931.3806451612902</v>
       </c>
       <c r="M77" s="1">
         <v>46185</v>
@@ -14289,11 +14291,11 @@
       </c>
       <c r="K78" s="2">
         <f t="shared" si="2"/>
-        <v>88.996763754045304</v>
+        <v>88.709677419354833</v>
       </c>
       <c r="L78" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2563.1067961165049</v>
+        <v>2554.838709677419</v>
       </c>
       <c r="M78" s="1">
         <v>46069</v>
@@ -14347,11 +14349,11 @@
       </c>
       <c r="K79" s="2">
         <f t="shared" si="2"/>
-        <v>88.996763754045304</v>
+        <v>88.709677419354833</v>
       </c>
       <c r="L79" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2516.8284789644013</v>
+        <v>2508.7096774193546</v>
       </c>
       <c r="M79" s="1">
         <v>46081</v>
@@ -14405,11 +14407,11 @@
       </c>
       <c r="K80" s="2">
         <f t="shared" si="2"/>
-        <v>88.996763754045304</v>
+        <v>88.709677419354833</v>
       </c>
       <c r="L80" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2563.1067961165049</v>
+        <v>2554.838709677419</v>
       </c>
       <c r="M80" s="1">
         <v>46088</v>
@@ -14463,11 +14465,11 @@
       </c>
       <c r="K81" s="2">
         <f t="shared" si="2"/>
-        <v>88.996763754045304</v>
+        <v>88.709677419354833</v>
       </c>
       <c r="L81" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2563.1067961165049</v>
+        <v>2554.838709677419</v>
       </c>
       <c r="M81" s="1">
         <v>46101</v>
@@ -14524,11 +14526,11 @@
       </c>
       <c r="K82" s="2">
         <f t="shared" si="2"/>
-        <v>88.996763754045304</v>
+        <v>88.709677419354833</v>
       </c>
       <c r="L82" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2491.9093851132684</v>
+        <v>2483.8709677419351</v>
       </c>
       <c r="M82" s="1">
         <v>46114</v>
@@ -14582,11 +14584,11 @@
       </c>
       <c r="K83" s="2">
         <f t="shared" si="2"/>
-        <v>88.996763754045304</v>
+        <v>88.709677419354833</v>
       </c>
       <c r="L83" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2456.3106796116504</v>
+        <v>2448.3870967741937</v>
       </c>
       <c r="M83" s="1">
         <v>46129</v>
@@ -14643,11 +14645,11 @@
       </c>
       <c r="K84" s="2">
         <f t="shared" si="2"/>
-        <v>88.996763754045304</v>
+        <v>88.709677419354833</v>
       </c>
       <c r="L84" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1317.1521035598705</v>
+        <v>1312.9032258064517</v>
       </c>
       <c r="M84" s="1">
         <v>46153</v>
@@ -14698,11 +14700,11 @@
       </c>
       <c r="K85" s="2">
         <f t="shared" si="2"/>
-        <v>100.32362459546925</v>
+        <v>100</v>
       </c>
       <c r="L85" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1484.789644012945</v>
+        <v>1480</v>
       </c>
       <c r="M85" s="1">
         <v>46153</v>
@@ -16241,11 +16243,11 @@
         <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</f>
         <v>0.85</v>
       </c>
-      <c r="K112" s="43">
+      <c r="K112" s="2">
         <f>IF(I112="$", J112/$H$1, IF(I112="U$D", J112*1, 0))</f>
         <v>0.85</v>
       </c>
-      <c r="L112" s="43">
+      <c r="L112" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
         <v>1700</v>
       </c>
@@ -16347,11 +16349,11 @@
       </c>
       <c r="K114" s="2">
         <f>IF(I114="$", J114/$H$1, IF(I114="U$D", J114*1, 0))</f>
-        <v>65.372168284789637</v>
+        <v>65.161290322580641</v>
       </c>
       <c r="L114" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2010.8478964401293</v>
+        <v>2004.3612903225805</v>
       </c>
       <c r="M114" s="1">
         <v>46254</v>

--- a/public/data/pedido quimicos campaña 2026 valorizado.xlsx
+++ b/public/data/pedido quimicos campaña 2026 valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fincalaseis-my.sharepoint.com/personal/compras_fincalaseis_com_ar/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2197" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE95267E-728D-4B74-83FB-668C9B036283}"/>
+  <xr:revisionPtr revIDLastSave="2200" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F1390D7-D597-4D10-8543-3F26C9F56054}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8EF26D9B-9BDD-40EA-9926-EAD75B18C35F}"/>
   </bookViews>
@@ -32,7 +32,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId13"/>
+    <pivotCache cacheId="3" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="191">
   <si>
     <t>Solicita</t>
   </si>
@@ -336,9 +336,6 @@
   </si>
   <si>
     <t>Proquimica</t>
-  </si>
-  <si>
-    <t>Quiroga</t>
   </si>
   <si>
     <t>Etiquetas de fila</t>
@@ -633,6 +630,12 @@
   </si>
   <si>
     <t>R-1-577</t>
+  </si>
+  <si>
+    <t>Olivera Daniel</t>
+  </si>
+  <si>
+    <t>R-1-597</t>
   </si>
 </sst>
 </file>
@@ -4521,7 +4524,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:F4" firstHeaderRow="0" firstDataRow="1" firstDataCol="4"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5163,7 +5166,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:E12" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5850,7 +5853,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:D22" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -6537,7 +6540,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:G22" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -7270,7 +7273,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:G66" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -8173,7 +8176,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:E63" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -9047,7 +9050,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -10146,7 +10149,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="G1" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H1" s="8">
         <v>1550</v>
@@ -10170,7 +10173,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J3" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K3" s="27">
         <f>SUM(L3:M3)</f>
@@ -10187,7 +10190,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J4" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K4" s="30">
         <f>SUM(L4:M4)</f>
@@ -10195,11 +10198,11 @@
       </c>
       <c r="L4" s="31">
         <f>SUMIFS(L:L, H:H, "PRODUCCION DE PASTA", O:O, "Cumplido")</f>
-        <v>53506.511799999986</v>
+        <v>55206.511799999986</v>
       </c>
       <c r="M4" s="32">
         <f>SUMIFS(L:L, H:H, "PRODUCCION DE PASTA", O:O, "Pendiente")</f>
-        <v>3815.7</v>
+        <v>2115.6999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10209,7 +10212,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J6" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K6" s="34">
         <f>SUM(K3:K5)</f>
@@ -10217,16 +10220,16 @@
       </c>
       <c r="L6" s="34">
         <f>SUM(L3:L5)</f>
-        <v>368077.91825161286</v>
+        <v>369777.91825161286</v>
       </c>
       <c r="M6" s="35">
         <f>SUM(M3:M5)</f>
-        <v>3815.7</v>
+        <v>2115.6999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J7" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K7" s="36">
         <f>K6*H1</f>
@@ -10234,11 +10237,11 @@
       </c>
       <c r="L7" s="36">
         <f>L6*H1</f>
-        <v>570520773.28999996</v>
+        <v>573155773.28999996</v>
       </c>
       <c r="M7" s="37">
         <f>M6*H1</f>
-        <v>5914335</v>
+        <v>3279334.9999999995</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -10572,7 +10575,7 @@
         <v>31</v>
       </c>
       <c r="P14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -10633,7 +10636,7 @@
         <v>31</v>
       </c>
       <c r="P15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -10688,7 +10691,7 @@
         <v>31</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -10853,7 +10856,7 @@
         <v>31</v>
       </c>
       <c r="P19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q19">
         <v>4</v>
@@ -11059,7 +11062,7 @@
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H23" t="s">
         <v>83</v>
@@ -11091,7 +11094,7 @@
         <v>31</v>
       </c>
       <c r="P23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -11120,7 +11123,7 @@
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H24" t="s">
         <v>83</v>
@@ -11152,7 +11155,7 @@
         <v>31</v>
       </c>
       <c r="P24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q24">
         <v>4</v>
@@ -11181,7 +11184,7 @@
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H25" t="s">
         <v>83</v>
@@ -11213,7 +11216,7 @@
         <v>31</v>
       </c>
       <c r="P25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
@@ -11268,7 +11271,7 @@
         <v>31</v>
       </c>
       <c r="P26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -11323,7 +11326,7 @@
         <v>31</v>
       </c>
       <c r="P27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -11378,7 +11381,7 @@
         <v>31</v>
       </c>
       <c r="P28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -11491,7 +11494,7 @@
         <v>31</v>
       </c>
       <c r="P30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -11552,7 +11555,7 @@
         <v>31</v>
       </c>
       <c r="P31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q31">
         <v>4</v>
@@ -11668,7 +11671,7 @@
         <v>31</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -11723,7 +11726,7 @@
         <v>31</v>
       </c>
       <c r="P34" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -11940,7 +11943,7 @@
         <v>31</v>
       </c>
       <c r="P38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -11995,7 +11998,7 @@
         <v>31</v>
       </c>
       <c r="P39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q39">
         <v>4</v>
@@ -12056,7 +12059,7 @@
         <v>31</v>
       </c>
       <c r="P40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -12111,7 +12114,7 @@
         <v>31</v>
       </c>
       <c r="P41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -12128,7 +12131,7 @@
         <v>36.03</v>
       </c>
       <c r="E42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
@@ -12186,7 +12189,7 @@
         <v>36.03</v>
       </c>
       <c r="E43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F43" t="s">
         <v>39</v>
@@ -12244,7 +12247,7 @@
         <v>36.78</v>
       </c>
       <c r="E44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
@@ -12302,7 +12305,7 @@
         <v>36.78</v>
       </c>
       <c r="E45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
@@ -12360,7 +12363,7 @@
         <v>26.54</v>
       </c>
       <c r="E46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F46" t="s">
         <v>39</v>
@@ -12418,7 +12421,7 @@
         <v>33.200000000000003</v>
       </c>
       <c r="E47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
@@ -12476,7 +12479,7 @@
         <v>34.200000000000003</v>
       </c>
       <c r="E48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F48" t="s">
         <v>39</v>
@@ -12534,7 +12537,7 @@
         <v>35.880000000000003</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F49" t="s">
         <v>39</v>
@@ -12592,7 +12595,7 @@
         <v>34.299999999999997</v>
       </c>
       <c r="E50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F50" t="s">
         <v>39</v>
@@ -12650,7 +12653,7 @@
         <v>39.299999999999997</v>
       </c>
       <c r="E51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F51" t="s">
         <v>39</v>
@@ -12708,7 +12711,7 @@
         <v>27.96</v>
       </c>
       <c r="E52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
@@ -12766,7 +12769,7 @@
         <v>30.58</v>
       </c>
       <c r="E53" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F53" t="s">
         <v>39</v>
@@ -12824,7 +12827,7 @@
         <v>31.62</v>
       </c>
       <c r="E54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
@@ -12862,7 +12865,7 @@
         <v>31</v>
       </c>
       <c r="P54" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12885,7 +12888,7 @@
         <v>28</v>
       </c>
       <c r="E55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F55" t="s">
         <v>39</v>
@@ -12923,7 +12926,7 @@
         <v>31</v>
       </c>
       <c r="P55" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q55">
         <v>4</v>
@@ -12946,7 +12949,7 @@
         <v>37.96</v>
       </c>
       <c r="E56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F56" t="s">
         <v>39</v>
@@ -12984,7 +12987,7 @@
         <v>31</v>
       </c>
       <c r="P56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q56">
         <v>4</v>
@@ -13007,7 +13010,7 @@
         <v>30.16</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F57" t="s">
         <v>39</v>
@@ -13045,7 +13048,7 @@
         <v>31</v>
       </c>
       <c r="P57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q57">
         <v>4</v>
@@ -13068,7 +13071,7 @@
         <v>31.54</v>
       </c>
       <c r="E58" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F58" t="s">
         <v>39</v>
@@ -13106,7 +13109,7 @@
         <v>31</v>
       </c>
       <c r="P58" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -13129,7 +13132,7 @@
         <v>35.44</v>
       </c>
       <c r="E59" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F59" t="s">
         <v>39</v>
@@ -13167,7 +13170,7 @@
         <v>31</v>
       </c>
       <c r="P59" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13190,7 +13193,7 @@
         <v>34.1</v>
       </c>
       <c r="E60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F60" t="s">
         <v>39</v>
@@ -13228,7 +13231,7 @@
         <v>31</v>
       </c>
       <c r="P60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13251,7 +13254,7 @@
         <v>36.36</v>
       </c>
       <c r="E61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F61" t="s">
         <v>39</v>
@@ -13289,7 +13292,7 @@
         <v>31</v>
       </c>
       <c r="P61" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13312,7 +13315,7 @@
         <v>30</v>
       </c>
       <c r="E62" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F62" t="s">
         <v>39</v>
@@ -13350,7 +13353,7 @@
         <v>31</v>
       </c>
       <c r="P62" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13373,7 +13376,7 @@
         <v>36.96</v>
       </c>
       <c r="E63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F63" t="s">
         <v>39</v>
@@ -13411,7 +13414,7 @@
         <v>31</v>
       </c>
       <c r="P63" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -13434,7 +13437,7 @@
         <v>32.42</v>
       </c>
       <c r="E64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F64" t="s">
         <v>39</v>
@@ -13472,7 +13475,7 @@
         <v>31</v>
       </c>
       <c r="P64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q64">
         <v>4</v>
@@ -13495,7 +13498,7 @@
         <v>33.78</v>
       </c>
       <c r="E65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F65" t="s">
         <v>39</v>
@@ -13533,7 +13536,7 @@
         <v>31</v>
       </c>
       <c r="P65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -13556,7 +13559,7 @@
         <v>30.2</v>
       </c>
       <c r="E66" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F66" t="s">
         <v>39</v>
@@ -13594,7 +13597,7 @@
         <v>31</v>
       </c>
       <c r="P66" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -13617,7 +13620,7 @@
         <v>32.32</v>
       </c>
       <c r="E67" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F67" t="s">
         <v>39</v>
@@ -13655,7 +13658,7 @@
         <v>31</v>
       </c>
       <c r="P67" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q67">
         <v>4</v>
@@ -13678,7 +13681,7 @@
         <v>32.06</v>
       </c>
       <c r="E68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F68" t="s">
         <v>39</v>
@@ -13716,7 +13719,7 @@
         <v>31</v>
       </c>
       <c r="P68" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -13739,7 +13742,7 @@
         <v>29.92</v>
       </c>
       <c r="E69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F69" t="s">
         <v>39</v>
@@ -13777,7 +13780,7 @@
         <v>31</v>
       </c>
       <c r="P69" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -13800,7 +13803,7 @@
         <v>28.14</v>
       </c>
       <c r="E70" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F70" t="s">
         <v>39</v>
@@ -13838,7 +13841,7 @@
         <v>31</v>
       </c>
       <c r="P70" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q70">
         <v>4</v>
@@ -13861,7 +13864,7 @@
         <v>28.8</v>
       </c>
       <c r="E71" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F71" t="s">
         <v>39</v>
@@ -13899,7 +13902,7 @@
         <v>31</v>
       </c>
       <c r="P71" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q71">
         <v>4</v>
@@ -13922,7 +13925,7 @@
         <v>29.36</v>
       </c>
       <c r="E72" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F72" t="s">
         <v>39</v>
@@ -13960,7 +13963,7 @@
         <v>31</v>
       </c>
       <c r="P72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -13983,7 +13986,7 @@
         <v>29.66</v>
       </c>
       <c r="E73" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F73" t="s">
         <v>39</v>
@@ -14021,7 +14024,7 @@
         <v>31</v>
       </c>
       <c r="P73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -14044,7 +14047,7 @@
         <v>31.3</v>
       </c>
       <c r="E74" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F74" t="s">
         <v>39</v>
@@ -14082,7 +14085,7 @@
         <v>31</v>
       </c>
       <c r="P74" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q74">
         <v>4</v>
@@ -14105,7 +14108,7 @@
         <v>28.38</v>
       </c>
       <c r="E75" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F75" t="s">
         <v>39</v>
@@ -14143,7 +14146,7 @@
         <v>31</v>
       </c>
       <c r="P75" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -14160,7 +14163,7 @@
         <v>32.119999999999997</v>
       </c>
       <c r="E76" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F76" t="s">
         <v>39</v>
@@ -14198,7 +14201,7 @@
         <v>31</v>
       </c>
       <c r="P76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -14215,7 +14218,7 @@
         <v>29.64</v>
       </c>
       <c r="E77" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F77" t="s">
         <v>39</v>
@@ -14253,7 +14256,7 @@
         <v>31</v>
       </c>
       <c r="P77" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -14270,7 +14273,7 @@
         <v>28.8</v>
       </c>
       <c r="E78" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F78" t="s">
         <v>43</v>
@@ -14328,7 +14331,7 @@
         <v>28.28</v>
       </c>
       <c r="E79" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F79" t="s">
         <v>43</v>
@@ -14386,7 +14389,7 @@
         <v>28.8</v>
       </c>
       <c r="E80" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F80" t="s">
         <v>43</v>
@@ -14444,7 +14447,7 @@
         <v>28.8</v>
       </c>
       <c r="E81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F81" t="s">
         <v>43</v>
@@ -14482,7 +14485,7 @@
         <v>31</v>
       </c>
       <c r="P81" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q81">
         <v>4</v>
@@ -14505,7 +14508,7 @@
         <v>28</v>
       </c>
       <c r="E82" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F82" t="s">
         <v>43</v>
@@ -14563,7 +14566,7 @@
         <v>27.6</v>
       </c>
       <c r="E83" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F83" t="s">
         <v>43</v>
@@ -14601,7 +14604,7 @@
         <v>31</v>
       </c>
       <c r="P83" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q83">
         <v>4</v>
@@ -14624,7 +14627,7 @@
         <v>14.8</v>
       </c>
       <c r="E84" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F84" t="s">
         <v>43</v>
@@ -14662,7 +14665,7 @@
         <v>31</v>
       </c>
       <c r="P84" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
@@ -14679,10 +14682,10 @@
         <v>14.8</v>
       </c>
       <c r="E85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F85" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G85" t="s">
         <v>40</v>
@@ -14717,7 +14720,7 @@
         <v>31</v>
       </c>
       <c r="P85" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
@@ -14882,7 +14885,7 @@
         <v>31</v>
       </c>
       <c r="P88" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
@@ -14905,7 +14908,7 @@
         <v>46</v>
       </c>
       <c r="G89" t="s">
-        <v>91</v>
+        <v>189</v>
       </c>
       <c r="H89" t="s">
         <v>52</v>
@@ -14957,7 +14960,7 @@
         <v>46</v>
       </c>
       <c r="G90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H90" t="s">
         <v>52</v>
@@ -15015,7 +15018,7 @@
         <v>46</v>
       </c>
       <c r="G91" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H91" t="s">
         <v>52</v>
@@ -15047,7 +15050,7 @@
         <v>31</v>
       </c>
       <c r="P91" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -15076,7 +15079,7 @@
         <v>46</v>
       </c>
       <c r="G92" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H92" t="s">
         <v>52</v>
@@ -15282,7 +15285,7 @@
         <v>31</v>
       </c>
       <c r="P95" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -15343,7 +15346,7 @@
         <v>31</v>
       </c>
       <c r="P96" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -15404,7 +15407,7 @@
         <v>31</v>
       </c>
       <c r="P97" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
@@ -15459,7 +15462,7 @@
         <v>31</v>
       </c>
       <c r="P98" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
@@ -15514,7 +15517,7 @@
         <v>31</v>
       </c>
       <c r="P99" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
@@ -15569,7 +15572,7 @@
         <v>31</v>
       </c>
       <c r="P100" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
@@ -15682,7 +15685,7 @@
         <v>31</v>
       </c>
       <c r="P102" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
@@ -15737,7 +15740,7 @@
         <v>31</v>
       </c>
       <c r="P103" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
@@ -15792,7 +15795,7 @@
         <v>31</v>
       </c>
       <c r="P104" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
@@ -15847,7 +15850,7 @@
         <v>31</v>
       </c>
       <c r="P105" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
@@ -15870,7 +15873,7 @@
         <v>49</v>
       </c>
       <c r="G106" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H106" t="s">
         <v>52</v>
@@ -15902,7 +15905,7 @@
         <v>31</v>
       </c>
       <c r="P106" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q106">
         <v>4</v>
@@ -15931,7 +15934,7 @@
         <v>49</v>
       </c>
       <c r="G107" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H107" t="s">
         <v>52</v>
@@ -15963,7 +15966,7 @@
         <v>31</v>
       </c>
       <c r="P107" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -15992,7 +15995,7 @@
         <v>49</v>
       </c>
       <c r="G108" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H108" t="s">
         <v>52</v>
@@ -16024,7 +16027,7 @@
         <v>31</v>
       </c>
       <c r="P108" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q108">
         <v>4</v>
@@ -16053,7 +16056,7 @@
         <v>46</v>
       </c>
       <c r="G109" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H109" t="s">
         <v>52</v>
@@ -16085,7 +16088,7 @@
         <v>31</v>
       </c>
       <c r="P109" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -16146,7 +16149,7 @@
         <v>31</v>
       </c>
       <c r="P110" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
@@ -16201,7 +16204,7 @@
         <v>31</v>
       </c>
       <c r="P111" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q111">
         <v>4</v>
@@ -16259,7 +16262,10 @@
         <v>septiembre</v>
       </c>
       <c r="O112" t="s">
-        <v>24</v>
+        <v>31</v>
+      </c>
+      <c r="P112" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
@@ -16282,7 +16288,7 @@
         <v>46</v>
       </c>
       <c r="G113" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H113" t="s">
         <v>52</v>
@@ -16328,10 +16334,10 @@
         <v>30.76</v>
       </c>
       <c r="E114" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F114" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G114" t="s">
         <v>40</v>
@@ -16366,7 +16372,7 @@
         <v>31</v>
       </c>
       <c r="P114" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -17085,7 +17091,7 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -17221,7 +17227,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B20">
         <v>14.8</v>
@@ -17634,10 +17640,10 @@
         <v>89</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -17931,7 +17937,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
@@ -17950,7 +17956,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
@@ -17992,10 +17998,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
@@ -18025,7 +18031,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F25" t="s">
         <v>86</v>
@@ -18040,10 +18046,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G26">
         <v>8000</v>
@@ -18097,7 +18103,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
         <v>57</v>
@@ -18249,7 +18255,7 @@
     </row>
     <row r="47" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -18430,7 +18436,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D17">
         <v>1198.58</v>
@@ -18441,7 +18447,7 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D18">
         <v>185.08</v>
@@ -18460,10 +18466,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D20">
         <v>14.8</v>
@@ -18778,7 +18784,7 @@
         <v>101000</v>
       </c>
       <c r="E17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F17">
         <v>1198.58</v>
@@ -18798,7 +18804,7 @@
         <v>137500</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F18">
         <v>185.08</v>
@@ -18829,7 +18835,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C20" t="s">
         <v>9</v>
@@ -18838,7 +18844,7 @@
         <v>155000</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F20">
         <v>14.8</v>
@@ -18952,7 +18958,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F7">
         <v>30</v>
@@ -19197,7 +19203,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F26">
         <v>23549</v>
@@ -19217,7 +19223,7 @@
         <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F27">
         <v>3000</v>
@@ -19234,7 +19240,7 @@
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F28">
         <v>1000</v>
@@ -19245,7 +19251,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F29">
         <v>4000</v>
@@ -19452,7 +19458,7 @@
         <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E45" t="s">
         <v>30</v>
@@ -19521,7 +19527,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E51" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F51">
         <v>30.76</v>
@@ -19535,7 +19541,7 @@
         <v>43</v>
       </c>
       <c r="D52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E52" t="s">
         <v>23</v>
@@ -19632,10 +19638,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E60" t="s">
         <v>42</v>
@@ -19649,7 +19655,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F61">
         <v>198268.46000000002</v>
@@ -19669,7 +19675,7 @@
         <v>19</v>
       </c>
       <c r="E62" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F62">
         <v>500</v>
@@ -19680,7 +19686,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F63">
         <v>500</v>
@@ -19782,7 +19788,7 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D6">
         <v>72.06</v>
@@ -19807,7 +19813,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D8">
         <v>44072.06</v>
@@ -19880,7 +19886,7 @@
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D13">
         <v>203.38</v>
@@ -19894,7 +19900,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D14">
         <v>57.08</v>
@@ -19933,7 +19939,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D17">
         <v>30954.460000000003</v>
@@ -20048,7 +20054,7 @@
         <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D25">
         <v>360.96000000000004</v>
@@ -20062,7 +20068,7 @@
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D26">
         <v>57.6</v>
@@ -20115,7 +20121,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30">
         <v>63693.56</v>
@@ -20188,7 +20194,7 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D35">
         <v>288.98</v>
@@ -20202,7 +20208,7 @@
         <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D36">
         <v>55.6</v>
@@ -20241,7 +20247,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>60444.58</v>
@@ -20328,7 +20334,7 @@
         <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D45">
         <v>212.8</v>
@@ -20342,7 +20348,7 @@
         <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D46">
         <v>14.8</v>
@@ -20365,7 +20371,7 @@
         <v>295</v>
       </c>
       <c r="H47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -20412,10 +20418,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D51">
         <v>14.8</v>
@@ -20426,7 +20432,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D52">
         <v>16227.399999999998</v>
@@ -20485,7 +20491,7 @@
         <v>39</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D56">
         <v>29.64</v>
@@ -20510,7 +20516,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D58">
         <v>6364.64</v>
@@ -20521,7 +20527,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B59" t="s">
         <v>49</v>
@@ -20538,7 +20544,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D60">
         <v>30</v>
@@ -20549,13 +20555,13 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B61" t="s">
         <v>39</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D61">
         <v>30.76</v>
@@ -20566,7 +20572,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D62">
         <v>30.76</v>
@@ -20617,22 +20623,22 @@
         <v>1</v>
       </c>
       <c r="C2" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="38" t="s">
         <v>106</v>
-      </c>
-      <c r="D2" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="E2" s="38" t="s">
-        <v>107</v>
       </c>
       <c r="F2" s="38" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" s="38" t="s">
         <v>109</v>
-      </c>
-      <c r="H2" s="38" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
@@ -20640,10 +20646,10 @@
         <v>46037</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E3" s="3">
         <v>72.06</v>
@@ -20665,10 +20671,10 @@
         <v>46051</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E4" s="3">
         <v>73.56</v>
@@ -20690,10 +20696,10 @@
         <v>46062</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E5" s="3">
         <v>26.54</v>
@@ -20715,10 +20721,10 @@
         <v>46062</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E6" s="3">
         <v>28.8</v>
@@ -20740,10 +20746,10 @@
         <v>46072</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="3">
         <v>33.200000000000003</v>
@@ -20765,10 +20771,10 @@
         <v>46077</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E8" s="3">
         <v>34.200000000000003</v>
@@ -20790,10 +20796,10 @@
         <v>46081</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E9" s="3">
         <v>28.28</v>
@@ -20815,10 +20821,10 @@
         <v>46081</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E10" s="3">
         <v>35.880000000000003</v>
@@ -20840,10 +20846,10 @@
         <v>46085</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E11" s="3">
         <v>34.299999999999997</v>
@@ -20865,10 +20871,10 @@
         <v>46091</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E12" s="3">
         <v>39.299999999999997</v>
@@ -20890,10 +20896,10 @@
         <v>46092</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E13" s="3">
         <v>28.8</v>
@@ -20915,10 +20921,10 @@
         <v>15.3</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E14" s="3">
         <v>27.96</v>
@@ -20940,10 +20946,10 @@
         <v>46096</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E15" s="3">
         <v>30.58</v>

--- a/public/data/pedido quimicos campaña 2026 valorizado.xlsx
+++ b/public/data/pedido quimicos campaña 2026 valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fincalaseis-my.sharepoint.com/personal/compras_fincalaseis_com_ar/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2200" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F1390D7-D597-4D10-8543-3F26C9F56054}"/>
+  <xr:revisionPtr revIDLastSave="2211" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAF530D6-0E04-4248-A962-BC36FDE30546}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8EF26D9B-9BDD-40EA-9926-EAD75B18C35F}"/>
   </bookViews>
@@ -32,7 +32,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId13"/>
+    <pivotCache cacheId="76" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="193">
   <si>
     <t>Solicita</t>
   </si>
@@ -636,6 +636,12 @@
   </si>
   <si>
     <t>R-1-597</t>
+  </si>
+  <si>
+    <t>R-1-300</t>
+  </si>
+  <si>
+    <t>R-1-304</t>
   </si>
 </sst>
 </file>
@@ -4524,7 +4530,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0AE0A6B-F6F9-40DC-9E47-D99F5BE06263}" name="TablaDinámica1" cacheId="76" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:F4" firstHeaderRow="0" firstDataRow="1" firstDataCol="4"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5166,7 +5172,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{054F9C9F-74B3-4A59-839B-505AD526C292}" name="TablaDinámica2" cacheId="76" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:E12" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5853,7 +5859,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57ED06CC-DD35-4C6F-808E-B8BD01C17501}" name="TablaDinámica4" cacheId="76" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:D22" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -6540,7 +6546,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5BB732F-4163-4A77-A29C-870C61A629E8}" name="TablaDinámica4" cacheId="76" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:G22" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -7273,7 +7279,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092B43AC-EFCE-43E3-AC57-3A545E2BAF78}" name="TablaDinámica2" cacheId="76" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:G66" firstHeaderRow="0" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -8176,7 +8182,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8665C329-CFF5-4C45-8D69-E036299DA91C}" name="TablaDinámica2" cacheId="76" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:E63" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="21">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -9050,7 +9056,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C439F056-EDB1-4476-9B4D-99E553F3A782}" name="TablaDinámica1" cacheId="76" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -9730,10 +9736,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}" name="Tabla1" displayName="Tabla1" ref="A9:S114" totalsRowShown="0" headerRowDxfId="45">
-  <autoFilter ref="A9:S114" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:S113">
-    <sortCondition ref="O9:O113"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}" name="Tabla1" displayName="Tabla1" ref="A9:S115" totalsRowShown="0" headerRowDxfId="45">
+  <autoFilter ref="A9:S115" xr:uid="{E5B47BA6-BB55-47E1-A3AB-D1FA729258E9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:S114">
+    <sortCondition ref="O9:O114"/>
   </sortState>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{ABC9D6B9-B435-44A8-AC1D-3A7F3684B351}" name="Solicita"/>
@@ -10124,7 +10130,7 @@
     <tabColor theme="6"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S114"/>
+  <dimension ref="A1:S115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -10194,15 +10200,15 @@
       </c>
       <c r="K4" s="30">
         <f>SUM(L4:M4)</f>
-        <v>57322.211799999983</v>
+        <v>57406.83979999998</v>
       </c>
       <c r="L4" s="31">
         <f>SUMIFS(L:L, H:H, "PRODUCCION DE PASTA", O:O, "Cumplido")</f>
-        <v>55206.511799999986</v>
+        <v>57406.83979999998</v>
       </c>
       <c r="M4" s="32">
         <f>SUMIFS(L:L, H:H, "PRODUCCION DE PASTA", O:O, "Pendiente")</f>
-        <v>2115.6999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10216,15 +10222,15 @@
       </c>
       <c r="K6" s="34">
         <f>SUM(K3:K5)</f>
-        <v>371893.61825161288</v>
+        <v>371978.24625161284</v>
       </c>
       <c r="L6" s="34">
         <f>SUM(L3:L5)</f>
-        <v>369777.91825161286</v>
+        <v>371978.24625161284</v>
       </c>
       <c r="M6" s="35">
         <f>SUM(M3:M5)</f>
-        <v>2115.6999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -10233,15 +10239,15 @@
       </c>
       <c r="K7" s="36">
         <f>K6*H1</f>
-        <v>576435108.28999996</v>
+        <v>576566281.68999994</v>
       </c>
       <c r="L7" s="36">
         <f>L6*H1</f>
-        <v>573155773.28999996</v>
+        <v>576566281.68999994</v>
       </c>
       <c r="M7" s="37">
         <f>M6*H1</f>
-        <v>3279334.9999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15948,7 +15954,7 @@
         <v>3.15</v>
       </c>
       <c r="K107" s="2">
-        <f t="shared" ref="K107:K113" si="3">IF(I107="$", J107/$H$1, IF(I107="U$D", J107*1, 0))</f>
+        <f t="shared" ref="K107:K114" si="3">IF(I107="$", J107/$H$1, IF(I107="U$D", J107*1, 0))</f>
         <v>3.15</v>
       </c>
       <c r="L107" s="2">
@@ -16279,7 +16285,7 @@
         <v>18</v>
       </c>
       <c r="D113">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="E113" t="s">
         <v>19</v>
@@ -16302,22 +16308,25 @@
         <v>2.1156999999999999</v>
       </c>
       <c r="K113" s="2">
-        <f t="shared" si="3"/>
+        <f>IF(I113="$", J113/$H$1, IF(I113="U$D", J113*1, 0))</f>
         <v>2.1156999999999999</v>
       </c>
       <c r="L113" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2115.6999999999998</v>
+        <v>1100.164</v>
       </c>
       <c r="M113" s="1">
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="N113" t="str">
         <f>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</f>
-        <v>septiembre</v>
+        <v>octubre</v>
       </c>
       <c r="O113" t="s">
-        <v>24</v>
+        <v>31</v>
+      </c>
+      <c r="P113" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
@@ -16325,58 +16334,113 @@
         <v>17</v>
       </c>
       <c r="B114" s="1">
-        <v>46253</v>
+        <v>46044</v>
       </c>
       <c r="C114" t="s">
         <v>18</v>
       </c>
       <c r="D114">
-        <v>30.76</v>
+        <v>520</v>
       </c>
       <c r="E114" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="F114" t="s">
-        <v>181</v>
+        <v>46</v>
       </c>
       <c r="G114" t="s">
-        <v>40</v>
+        <v>179</v>
       </c>
       <c r="H114" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="I114" s="3" t="str">
         <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[[Descripcion]:[Moneda]],3,FALSE)</f>
-        <v>$</v>
+        <v>U$D</v>
       </c>
       <c r="J114" s="2">
         <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</f>
-        <v>101000</v>
+        <v>2.1156999999999999</v>
       </c>
       <c r="K114" s="2">
-        <f>IF(I114="$", J114/$H$1, IF(I114="U$D", J114*1, 0))</f>
-        <v>65.161290322580641</v>
+        <f t="shared" si="3"/>
+        <v>2.1156999999999999</v>
       </c>
       <c r="L114" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2004.3612903225805</v>
+        <v>1100.164</v>
       </c>
       <c r="M114" s="1">
-        <v>46254</v>
+        <v>46314</v>
       </c>
       <c r="N114" t="str">
         <f>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</f>
-        <v>agosto</v>
+        <v>octubre</v>
       </c>
       <c r="O114" t="s">
         <v>31</v>
       </c>
       <c r="P114" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>17</v>
+      </c>
+      <c r="B115" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C115" t="s">
+        <v>18</v>
+      </c>
+      <c r="D115">
+        <v>30.76</v>
+      </c>
+      <c r="E115" t="s">
+        <v>123</v>
+      </c>
+      <c r="F115" t="s">
+        <v>181</v>
+      </c>
+      <c r="G115" t="s">
+        <v>40</v>
+      </c>
+      <c r="H115" t="s">
+        <v>83</v>
+      </c>
+      <c r="I115" s="3" t="str">
+        <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[[Descripcion]:[Moneda]],3,FALSE)</f>
+        <v>$</v>
+      </c>
+      <c r="J115" s="2">
+        <f>VLOOKUP(Tabla1[[#This Row],[Articulo]],Tabla2[],4,FALSE)</f>
+        <v>101000</v>
+      </c>
+      <c r="K115" s="2">
+        <f>IF(I115="$", J115/$H$1, IF(I115="U$D", J115*1, 0))</f>
+        <v>65.161290322580641</v>
+      </c>
+      <c r="L115" s="2">
+        <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
+        <v>2004.3612903225805</v>
+      </c>
+      <c r="M115" s="1">
+        <v>46254</v>
+      </c>
+      <c r="N115" t="str">
+        <f>TEXT(Tabla1[[#This Row],[Fecha Entrega]],"mmmm")</f>
+        <v>agosto</v>
+      </c>
+      <c r="O115" t="s">
+        <v>31</v>
+      </c>
+      <c r="P115" t="s">
         <v>182</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A10:P114">
+  <conditionalFormatting sqref="A10:P115">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$O10="cumplido"</formula>
     </cfRule>
